--- a/public_html/modules/transport/templates/migration-driver.xlsx
+++ b/public_html/modules/transport/templates/migration-driver.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27726"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marcos\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TI\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C256E22F-8408-451A-BC95-2126F587B50E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F13A5C1-6339-4648-92A8-CA1C759ACB48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{55DBCC80-70EF-485F-AEA1-F9AE5EEF69A7}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="24240" windowHeight="13140" activeTab="1" xr2:uid="{55DBCC80-70EF-485F-AEA1-F9AE5EEF69A7}"/>
   </bookViews>
   <sheets>
     <sheet name="vehicles" sheetId="1" r:id="rId1"/>
     <sheet name="driver" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>id</t>
   </si>
@@ -62,6 +62,9 @@
   </si>
   <si>
     <t>capacity</t>
+  </si>
+  <si>
+    <t>password</t>
   </si>
 </sst>
 </file>
@@ -12438,1286 +12441,1296 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D352F24-BF0E-405C-9847-7A4A26BC7600}">
-  <dimension ref="A1:E2144"/>
+  <dimension ref="A1:F2144"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="33.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="26.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="58.28515625" customWidth="1"/>
-    <col min="4" max="4" width="13" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="33.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="58.28515625" customWidth="1"/>
+    <col min="5" max="5" width="16.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" t="s">
         <v>2</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>3</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>4</v>
       </c>
-      <c r="D1" t="s">
-        <v>5</v>
+      <c r="E1" t="s">
+        <v>12</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="661" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E661" s="2"/>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
     </row>
-    <row r="1696" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C1696" s="4"/>
+    <row r="661" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F661" s="2"/>
     </row>
-    <row r="2003" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E2003" s="1"/>
+    <row r="1696" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D1696" s="4"/>
+      <c r="E1696" s="4"/>
     </row>
-    <row r="2099" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E2099" s="3"/>
+    <row r="2003" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F2003" s="1"/>
     </row>
-    <row r="2100" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E2100" s="3"/>
+    <row r="2099" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F2099" s="3"/>
     </row>
-    <row r="2101" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E2101" s="3"/>
+    <row r="2100" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F2100" s="3"/>
     </row>
-    <row r="2102" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E2102" s="3"/>
+    <row r="2101" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F2101" s="3"/>
     </row>
-    <row r="2105" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E2105" s="3"/>
+    <row r="2102" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F2102" s="3"/>
     </row>
-    <row r="2144" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C2144" s="4"/>
+    <row r="2105" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F2105" s="3"/>
+    </row>
+    <row r="2144" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D2144" s="4"/>
+      <c r="E2144" s="4"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="C1:C18 C20:C1048576 B19">
+  <conditionalFormatting sqref="D1:E18 D20:E1048576 C19">
     <cfRule type="duplicateValues" dxfId="1194" priority="1"/>
     <cfRule type="duplicateValues" dxfId="1193" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D18 D20:D2757 E19">
+  <conditionalFormatting sqref="F19 A2:A18 A20:A2757">
     <cfRule type="duplicateValues" dxfId="1192" priority="23"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D890">
-    <cfRule type="duplicateValues" dxfId="1191" priority="885"/>
-    <cfRule type="duplicateValues" dxfId="1190" priority="886"/>
-    <cfRule type="duplicateValues" dxfId="1189" priority="875"/>
-    <cfRule type="duplicateValues" dxfId="1188" priority="881"/>
-    <cfRule type="duplicateValues" dxfId="1187" priority="882"/>
-    <cfRule type="duplicateValues" dxfId="1186" priority="883"/>
-    <cfRule type="duplicateValues" dxfId="1185" priority="884"/>
-    <cfRule type="duplicateValues" dxfId="1184" priority="874"/>
-    <cfRule type="duplicateValues" dxfId="1183" priority="876"/>
-    <cfRule type="duplicateValues" dxfId="1182" priority="877"/>
-    <cfRule type="duplicateValues" dxfId="1181" priority="878"/>
-    <cfRule type="duplicateValues" dxfId="1180" priority="879"/>
-    <cfRule type="duplicateValues" dxfId="1179" priority="880"/>
+  <conditionalFormatting sqref="A890">
+    <cfRule type="duplicateValues" dxfId="1191" priority="874"/>
+    <cfRule type="duplicateValues" dxfId="1190" priority="875"/>
+    <cfRule type="duplicateValues" dxfId="1189" priority="876"/>
+    <cfRule type="duplicateValues" dxfId="1188" priority="877"/>
+    <cfRule type="duplicateValues" dxfId="1187" priority="878"/>
+    <cfRule type="duplicateValues" dxfId="1186" priority="879"/>
+    <cfRule type="duplicateValues" dxfId="1185" priority="880"/>
+    <cfRule type="duplicateValues" dxfId="1184" priority="881"/>
+    <cfRule type="duplicateValues" dxfId="1183" priority="882"/>
+    <cfRule type="duplicateValues" dxfId="1182" priority="883"/>
+    <cfRule type="duplicateValues" dxfId="1181" priority="884"/>
+    <cfRule type="duplicateValues" dxfId="1180" priority="885"/>
+    <cfRule type="duplicateValues" dxfId="1179" priority="886"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D962">
-    <cfRule type="duplicateValues" dxfId="1178" priority="989"/>
-    <cfRule type="duplicateValues" dxfId="1177" priority="990"/>
-    <cfRule type="duplicateValues" dxfId="1176" priority="991"/>
-    <cfRule type="duplicateValues" dxfId="1175" priority="992"/>
-    <cfRule type="duplicateValues" dxfId="1174" priority="993"/>
-    <cfRule type="duplicateValues" dxfId="1173" priority="986"/>
-    <cfRule type="duplicateValues" dxfId="1172" priority="983"/>
-    <cfRule type="duplicateValues" dxfId="1171" priority="984"/>
-    <cfRule type="duplicateValues" dxfId="1170" priority="985"/>
-    <cfRule type="duplicateValues" dxfId="1169" priority="987"/>
-    <cfRule type="duplicateValues" dxfId="1168" priority="988"/>
+  <conditionalFormatting sqref="A962">
+    <cfRule type="duplicateValues" dxfId="1178" priority="983"/>
+    <cfRule type="duplicateValues" dxfId="1177" priority="984"/>
+    <cfRule type="duplicateValues" dxfId="1176" priority="985"/>
+    <cfRule type="duplicateValues" dxfId="1175" priority="986"/>
+    <cfRule type="duplicateValues" dxfId="1174" priority="987"/>
+    <cfRule type="duplicateValues" dxfId="1173" priority="988"/>
+    <cfRule type="duplicateValues" dxfId="1172" priority="989"/>
+    <cfRule type="duplicateValues" dxfId="1171" priority="990"/>
+    <cfRule type="duplicateValues" dxfId="1170" priority="991"/>
+    <cfRule type="duplicateValues" dxfId="1169" priority="992"/>
+    <cfRule type="duplicateValues" dxfId="1168" priority="993"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D1995">
-    <cfRule type="duplicateValues" dxfId="1167" priority="1187"/>
-    <cfRule type="duplicateValues" dxfId="1166" priority="1186"/>
+  <conditionalFormatting sqref="A1995">
+    <cfRule type="duplicateValues" dxfId="1167" priority="1186"/>
+    <cfRule type="duplicateValues" dxfId="1166" priority="1187"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2000">
-    <cfRule type="duplicateValues" dxfId="1165" priority="1185"/>
-    <cfRule type="duplicateValues" dxfId="1164" priority="1184"/>
+  <conditionalFormatting sqref="A2000">
+    <cfRule type="duplicateValues" dxfId="1165" priority="1184"/>
+    <cfRule type="duplicateValues" dxfId="1164" priority="1185"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2003">
-    <cfRule type="duplicateValues" dxfId="1163" priority="1183"/>
-    <cfRule type="duplicateValues" dxfId="1162" priority="1182"/>
+  <conditionalFormatting sqref="A2003">
+    <cfRule type="duplicateValues" dxfId="1163" priority="1182"/>
+    <cfRule type="duplicateValues" dxfId="1162" priority="1183"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2014">
-    <cfRule type="duplicateValues" dxfId="1161" priority="1181"/>
-    <cfRule type="duplicateValues" dxfId="1160" priority="1180"/>
+  <conditionalFormatting sqref="A2014">
+    <cfRule type="duplicateValues" dxfId="1161" priority="1180"/>
+    <cfRule type="duplicateValues" dxfId="1160" priority="1181"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2018">
-    <cfRule type="duplicateValues" dxfId="1159" priority="1179"/>
-    <cfRule type="duplicateValues" dxfId="1158" priority="1178"/>
+  <conditionalFormatting sqref="A2018">
+    <cfRule type="duplicateValues" dxfId="1159" priority="1178"/>
+    <cfRule type="duplicateValues" dxfId="1158" priority="1179"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2020">
-    <cfRule type="duplicateValues" dxfId="1157" priority="1177"/>
-    <cfRule type="duplicateValues" dxfId="1156" priority="1176"/>
+  <conditionalFormatting sqref="A2020">
+    <cfRule type="duplicateValues" dxfId="1157" priority="1176"/>
+    <cfRule type="duplicateValues" dxfId="1156" priority="1177"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2033">
-    <cfRule type="duplicateValues" dxfId="1155" priority="1175"/>
-    <cfRule type="duplicateValues" dxfId="1154" priority="1174"/>
+  <conditionalFormatting sqref="A2033">
+    <cfRule type="duplicateValues" dxfId="1155" priority="1174"/>
+    <cfRule type="duplicateValues" dxfId="1154" priority="1175"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2035">
-    <cfRule type="duplicateValues" dxfId="1153" priority="1173"/>
-    <cfRule type="duplicateValues" dxfId="1152" priority="1172"/>
+  <conditionalFormatting sqref="A2035">
+    <cfRule type="duplicateValues" dxfId="1153" priority="1172"/>
+    <cfRule type="duplicateValues" dxfId="1152" priority="1173"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2059">
-    <cfRule type="duplicateValues" dxfId="1151" priority="1171"/>
-    <cfRule type="duplicateValues" dxfId="1150" priority="1170"/>
+  <conditionalFormatting sqref="A2059">
+    <cfRule type="duplicateValues" dxfId="1151" priority="1170"/>
+    <cfRule type="duplicateValues" dxfId="1150" priority="1171"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2060">
-    <cfRule type="duplicateValues" dxfId="1149" priority="1169"/>
-    <cfRule type="duplicateValues" dxfId="1148" priority="1168"/>
+  <conditionalFormatting sqref="A2060">
+    <cfRule type="duplicateValues" dxfId="1149" priority="1168"/>
+    <cfRule type="duplicateValues" dxfId="1148" priority="1169"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2061">
-    <cfRule type="duplicateValues" dxfId="1147" priority="1167"/>
-    <cfRule type="duplicateValues" dxfId="1146" priority="1166"/>
+  <conditionalFormatting sqref="A2061">
+    <cfRule type="duplicateValues" dxfId="1147" priority="1166"/>
+    <cfRule type="duplicateValues" dxfId="1146" priority="1167"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2079">
-    <cfRule type="duplicateValues" dxfId="1145" priority="1162"/>
-    <cfRule type="duplicateValues" dxfId="1144" priority="1161"/>
+  <conditionalFormatting sqref="A2079">
+    <cfRule type="duplicateValues" dxfId="1145" priority="1158"/>
+    <cfRule type="duplicateValues" dxfId="1144" priority="1159"/>
     <cfRule type="duplicateValues" dxfId="1143" priority="1160"/>
-    <cfRule type="duplicateValues" dxfId="1142" priority="1159"/>
-    <cfRule type="duplicateValues" dxfId="1141" priority="1158"/>
+    <cfRule type="duplicateValues" dxfId="1142" priority="1161"/>
+    <cfRule type="duplicateValues" dxfId="1141" priority="1162"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2080">
-    <cfRule type="duplicateValues" dxfId="1140" priority="1157"/>
-    <cfRule type="duplicateValues" dxfId="1139" priority="1156"/>
+  <conditionalFormatting sqref="A2080">
+    <cfRule type="duplicateValues" dxfId="1140" priority="1153"/>
+    <cfRule type="duplicateValues" dxfId="1139" priority="1154"/>
     <cfRule type="duplicateValues" dxfId="1138" priority="1155"/>
-    <cfRule type="duplicateValues" dxfId="1137" priority="1153"/>
-    <cfRule type="duplicateValues" dxfId="1136" priority="1154"/>
+    <cfRule type="duplicateValues" dxfId="1137" priority="1156"/>
+    <cfRule type="duplicateValues" dxfId="1136" priority="1157"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2083">
-    <cfRule type="duplicateValues" dxfId="1135" priority="1150"/>
-    <cfRule type="duplicateValues" dxfId="1134" priority="1151"/>
-    <cfRule type="duplicateValues" dxfId="1133" priority="1152"/>
-    <cfRule type="duplicateValues" dxfId="1132" priority="1149"/>
-    <cfRule type="duplicateValues" dxfId="1131" priority="1148"/>
+  <conditionalFormatting sqref="A2083">
+    <cfRule type="duplicateValues" dxfId="1135" priority="1148"/>
+    <cfRule type="duplicateValues" dxfId="1134" priority="1149"/>
+    <cfRule type="duplicateValues" dxfId="1133" priority="1150"/>
+    <cfRule type="duplicateValues" dxfId="1132" priority="1151"/>
+    <cfRule type="duplicateValues" dxfId="1131" priority="1152"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2084">
-    <cfRule type="duplicateValues" dxfId="1130" priority="1147"/>
+  <conditionalFormatting sqref="A2084">
+    <cfRule type="duplicateValues" dxfId="1130" priority="1143"/>
     <cfRule type="duplicateValues" dxfId="1129" priority="1144"/>
     <cfRule type="duplicateValues" dxfId="1128" priority="1145"/>
     <cfRule type="duplicateValues" dxfId="1127" priority="1146"/>
-    <cfRule type="duplicateValues" dxfId="1126" priority="1143"/>
+    <cfRule type="duplicateValues" dxfId="1126" priority="1147"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2085">
-    <cfRule type="duplicateValues" dxfId="1125" priority="1141"/>
-    <cfRule type="duplicateValues" dxfId="1124" priority="1142"/>
-    <cfRule type="duplicateValues" dxfId="1123" priority="1139"/>
-    <cfRule type="duplicateValues" dxfId="1122" priority="1140"/>
-    <cfRule type="duplicateValues" dxfId="1121" priority="1138"/>
+  <conditionalFormatting sqref="A2085">
+    <cfRule type="duplicateValues" dxfId="1125" priority="1138"/>
+    <cfRule type="duplicateValues" dxfId="1124" priority="1139"/>
+    <cfRule type="duplicateValues" dxfId="1123" priority="1140"/>
+    <cfRule type="duplicateValues" dxfId="1122" priority="1141"/>
+    <cfRule type="duplicateValues" dxfId="1121" priority="1142"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2086">
-    <cfRule type="duplicateValues" dxfId="1120" priority="1137"/>
-    <cfRule type="duplicateValues" dxfId="1119" priority="1136"/>
+  <conditionalFormatting sqref="A2086">
+    <cfRule type="duplicateValues" dxfId="1120" priority="1133"/>
+    <cfRule type="duplicateValues" dxfId="1119" priority="1134"/>
     <cfRule type="duplicateValues" dxfId="1118" priority="1135"/>
-    <cfRule type="duplicateValues" dxfId="1117" priority="1134"/>
-    <cfRule type="duplicateValues" dxfId="1116" priority="1133"/>
+    <cfRule type="duplicateValues" dxfId="1117" priority="1136"/>
+    <cfRule type="duplicateValues" dxfId="1116" priority="1137"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2087">
-    <cfRule type="duplicateValues" dxfId="1115" priority="1131"/>
-    <cfRule type="duplicateValues" dxfId="1114" priority="1130"/>
-    <cfRule type="duplicateValues" dxfId="1113" priority="1129"/>
-    <cfRule type="duplicateValues" dxfId="1112" priority="1128"/>
+  <conditionalFormatting sqref="A2087">
+    <cfRule type="duplicateValues" dxfId="1115" priority="1128"/>
+    <cfRule type="duplicateValues" dxfId="1114" priority="1129"/>
+    <cfRule type="duplicateValues" dxfId="1113" priority="1130"/>
+    <cfRule type="duplicateValues" dxfId="1112" priority="1131"/>
     <cfRule type="duplicateValues" dxfId="1111" priority="1132"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2088">
-    <cfRule type="duplicateValues" dxfId="1110" priority="1126"/>
-    <cfRule type="duplicateValues" dxfId="1109" priority="1125"/>
-    <cfRule type="duplicateValues" dxfId="1108" priority="1124"/>
-    <cfRule type="duplicateValues" dxfId="1107" priority="1123"/>
+  <conditionalFormatting sqref="A2088">
+    <cfRule type="duplicateValues" dxfId="1110" priority="1123"/>
+    <cfRule type="duplicateValues" dxfId="1109" priority="1124"/>
+    <cfRule type="duplicateValues" dxfId="1108" priority="1125"/>
+    <cfRule type="duplicateValues" dxfId="1107" priority="1126"/>
     <cfRule type="duplicateValues" dxfId="1106" priority="1127"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2092">
-    <cfRule type="duplicateValues" dxfId="1105" priority="1121"/>
-    <cfRule type="duplicateValues" dxfId="1104" priority="1120"/>
-    <cfRule type="duplicateValues" dxfId="1103" priority="1119"/>
-    <cfRule type="duplicateValues" dxfId="1102" priority="1118"/>
+  <conditionalFormatting sqref="A2092">
+    <cfRule type="duplicateValues" dxfId="1105" priority="1118"/>
+    <cfRule type="duplicateValues" dxfId="1104" priority="1119"/>
+    <cfRule type="duplicateValues" dxfId="1103" priority="1120"/>
+    <cfRule type="duplicateValues" dxfId="1102" priority="1121"/>
     <cfRule type="duplicateValues" dxfId="1101" priority="1122"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2100">
-    <cfRule type="duplicateValues" dxfId="1100" priority="1117"/>
-    <cfRule type="duplicateValues" dxfId="1099" priority="1116"/>
+  <conditionalFormatting sqref="A2100">
+    <cfRule type="duplicateValues" dxfId="1100" priority="1113"/>
+    <cfRule type="duplicateValues" dxfId="1099" priority="1114"/>
     <cfRule type="duplicateValues" dxfId="1098" priority="1115"/>
-    <cfRule type="duplicateValues" dxfId="1097" priority="1114"/>
-    <cfRule type="duplicateValues" dxfId="1096" priority="1113"/>
+    <cfRule type="duplicateValues" dxfId="1097" priority="1116"/>
+    <cfRule type="duplicateValues" dxfId="1096" priority="1117"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2101">
-    <cfRule type="duplicateValues" dxfId="1095" priority="1112"/>
-    <cfRule type="duplicateValues" dxfId="1094" priority="1111"/>
+  <conditionalFormatting sqref="A2101">
+    <cfRule type="duplicateValues" dxfId="1095" priority="1108"/>
+    <cfRule type="duplicateValues" dxfId="1094" priority="1109"/>
     <cfRule type="duplicateValues" dxfId="1093" priority="1110"/>
-    <cfRule type="duplicateValues" dxfId="1092" priority="1109"/>
-    <cfRule type="duplicateValues" dxfId="1091" priority="1108"/>
+    <cfRule type="duplicateValues" dxfId="1092" priority="1111"/>
+    <cfRule type="duplicateValues" dxfId="1091" priority="1112"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2116">
-    <cfRule type="duplicateValues" dxfId="1090" priority="1105"/>
-    <cfRule type="duplicateValues" dxfId="1089" priority="1104"/>
-    <cfRule type="duplicateValues" dxfId="1088" priority="1102"/>
-    <cfRule type="duplicateValues" dxfId="1087" priority="1101"/>
-    <cfRule type="duplicateValues" dxfId="1086" priority="1106"/>
-    <cfRule type="duplicateValues" dxfId="1085" priority="1103"/>
+  <conditionalFormatting sqref="A2116">
+    <cfRule type="duplicateValues" dxfId="1090" priority="1101"/>
+    <cfRule type="duplicateValues" dxfId="1089" priority="1102"/>
+    <cfRule type="duplicateValues" dxfId="1088" priority="1103"/>
+    <cfRule type="duplicateValues" dxfId="1087" priority="1104"/>
+    <cfRule type="duplicateValues" dxfId="1086" priority="1105"/>
+    <cfRule type="duplicateValues" dxfId="1085" priority="1106"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2143">
-    <cfRule type="duplicateValues" dxfId="1084" priority="1097"/>
-    <cfRule type="duplicateValues" dxfId="1083" priority="1096"/>
+  <conditionalFormatting sqref="A2143">
+    <cfRule type="duplicateValues" dxfId="1084" priority="1093"/>
+    <cfRule type="duplicateValues" dxfId="1083" priority="1094"/>
     <cfRule type="duplicateValues" dxfId="1082" priority="1095"/>
-    <cfRule type="duplicateValues" dxfId="1081" priority="1094"/>
-    <cfRule type="duplicateValues" dxfId="1080" priority="1093"/>
-    <cfRule type="duplicateValues" dxfId="1079" priority="1099"/>
-    <cfRule type="duplicateValues" dxfId="1078" priority="1098"/>
+    <cfRule type="duplicateValues" dxfId="1081" priority="1096"/>
+    <cfRule type="duplicateValues" dxfId="1080" priority="1097"/>
+    <cfRule type="duplicateValues" dxfId="1079" priority="1098"/>
+    <cfRule type="duplicateValues" dxfId="1078" priority="1099"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2144">
-    <cfRule type="duplicateValues" dxfId="1077" priority="1092"/>
-    <cfRule type="duplicateValues" dxfId="1076" priority="1091"/>
-    <cfRule type="duplicateValues" dxfId="1075" priority="1090"/>
-    <cfRule type="duplicateValues" dxfId="1074" priority="1083"/>
-    <cfRule type="duplicateValues" dxfId="1073" priority="1084"/>
-    <cfRule type="duplicateValues" dxfId="1072" priority="1081"/>
-    <cfRule type="duplicateValues" dxfId="1071" priority="1087"/>
-    <cfRule type="duplicateValues" dxfId="1070" priority="1088"/>
-    <cfRule type="duplicateValues" dxfId="1069" priority="1089"/>
-    <cfRule type="duplicateValues" dxfId="1068" priority="1086"/>
-    <cfRule type="duplicateValues" dxfId="1067" priority="1082"/>
-    <cfRule type="duplicateValues" dxfId="1066" priority="1080"/>
-    <cfRule type="duplicateValues" dxfId="1065" priority="1079"/>
-    <cfRule type="duplicateValues" dxfId="1064" priority="1078"/>
+  <conditionalFormatting sqref="A2144">
+    <cfRule type="duplicateValues" dxfId="1077" priority="1078"/>
+    <cfRule type="duplicateValues" dxfId="1076" priority="1079"/>
+    <cfRule type="duplicateValues" dxfId="1075" priority="1080"/>
+    <cfRule type="duplicateValues" dxfId="1074" priority="1081"/>
+    <cfRule type="duplicateValues" dxfId="1073" priority="1082"/>
+    <cfRule type="duplicateValues" dxfId="1072" priority="1083"/>
+    <cfRule type="duplicateValues" dxfId="1071" priority="1084"/>
+    <cfRule type="duplicateValues" dxfId="1070" priority="1086"/>
+    <cfRule type="duplicateValues" dxfId="1069" priority="1087"/>
+    <cfRule type="duplicateValues" dxfId="1068" priority="1088"/>
+    <cfRule type="duplicateValues" dxfId="1067" priority="1089"/>
+    <cfRule type="duplicateValues" dxfId="1066" priority="1090"/>
+    <cfRule type="duplicateValues" dxfId="1065" priority="1091"/>
+    <cfRule type="duplicateValues" dxfId="1064" priority="1092"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2145">
-    <cfRule type="duplicateValues" dxfId="1063" priority="1071"/>
-    <cfRule type="duplicateValues" dxfId="1062" priority="1069"/>
-    <cfRule type="duplicateValues" dxfId="1061" priority="1068"/>
-    <cfRule type="duplicateValues" dxfId="1060" priority="1067"/>
-    <cfRule type="duplicateValues" dxfId="1059" priority="1066"/>
-    <cfRule type="duplicateValues" dxfId="1058" priority="1065"/>
-    <cfRule type="duplicateValues" dxfId="1057" priority="1064"/>
-    <cfRule type="duplicateValues" dxfId="1056" priority="1063"/>
-    <cfRule type="duplicateValues" dxfId="1055" priority="1070"/>
-    <cfRule type="duplicateValues" dxfId="1054" priority="1075"/>
-    <cfRule type="duplicateValues" dxfId="1053" priority="1074"/>
-    <cfRule type="duplicateValues" dxfId="1052" priority="1073"/>
-    <cfRule type="duplicateValues" dxfId="1051" priority="1072"/>
-    <cfRule type="duplicateValues" dxfId="1050" priority="1077"/>
-    <cfRule type="duplicateValues" dxfId="1049" priority="1076"/>
+  <conditionalFormatting sqref="A2145">
+    <cfRule type="duplicateValues" dxfId="1063" priority="1063"/>
+    <cfRule type="duplicateValues" dxfId="1062" priority="1064"/>
+    <cfRule type="duplicateValues" dxfId="1061" priority="1065"/>
+    <cfRule type="duplicateValues" dxfId="1060" priority="1066"/>
+    <cfRule type="duplicateValues" dxfId="1059" priority="1067"/>
+    <cfRule type="duplicateValues" dxfId="1058" priority="1068"/>
+    <cfRule type="duplicateValues" dxfId="1057" priority="1069"/>
+    <cfRule type="duplicateValues" dxfId="1056" priority="1070"/>
+    <cfRule type="duplicateValues" dxfId="1055" priority="1071"/>
+    <cfRule type="duplicateValues" dxfId="1054" priority="1072"/>
+    <cfRule type="duplicateValues" dxfId="1053" priority="1073"/>
+    <cfRule type="duplicateValues" dxfId="1052" priority="1074"/>
+    <cfRule type="duplicateValues" dxfId="1051" priority="1075"/>
+    <cfRule type="duplicateValues" dxfId="1050" priority="1076"/>
+    <cfRule type="duplicateValues" dxfId="1049" priority="1077"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2146">
-    <cfRule type="duplicateValues" dxfId="1048" priority="1055"/>
-    <cfRule type="duplicateValues" dxfId="1047" priority="1056"/>
-    <cfRule type="duplicateValues" dxfId="1046" priority="1057"/>
-    <cfRule type="duplicateValues" dxfId="1045" priority="1058"/>
-    <cfRule type="duplicateValues" dxfId="1044" priority="1059"/>
-    <cfRule type="duplicateValues" dxfId="1043" priority="1060"/>
-    <cfRule type="duplicateValues" dxfId="1042" priority="1061"/>
-    <cfRule type="duplicateValues" dxfId="1041" priority="1062"/>
-    <cfRule type="duplicateValues" dxfId="1040" priority="1052"/>
-    <cfRule type="duplicateValues" dxfId="1039" priority="1053"/>
-    <cfRule type="duplicateValues" dxfId="1038" priority="1051"/>
-    <cfRule type="duplicateValues" dxfId="1037" priority="1050"/>
-    <cfRule type="duplicateValues" dxfId="1036" priority="1049"/>
-    <cfRule type="duplicateValues" dxfId="1035" priority="1048"/>
-    <cfRule type="duplicateValues" dxfId="1034" priority="1054"/>
+  <conditionalFormatting sqref="A2146">
+    <cfRule type="duplicateValues" dxfId="1048" priority="1048"/>
+    <cfRule type="duplicateValues" dxfId="1047" priority="1049"/>
+    <cfRule type="duplicateValues" dxfId="1046" priority="1050"/>
+    <cfRule type="duplicateValues" dxfId="1045" priority="1051"/>
+    <cfRule type="duplicateValues" dxfId="1044" priority="1052"/>
+    <cfRule type="duplicateValues" dxfId="1043" priority="1053"/>
+    <cfRule type="duplicateValues" dxfId="1042" priority="1054"/>
+    <cfRule type="duplicateValues" dxfId="1041" priority="1055"/>
+    <cfRule type="duplicateValues" dxfId="1040" priority="1056"/>
+    <cfRule type="duplicateValues" dxfId="1039" priority="1057"/>
+    <cfRule type="duplicateValues" dxfId="1038" priority="1058"/>
+    <cfRule type="duplicateValues" dxfId="1037" priority="1059"/>
+    <cfRule type="duplicateValues" dxfId="1036" priority="1060"/>
+    <cfRule type="duplicateValues" dxfId="1035" priority="1061"/>
+    <cfRule type="duplicateValues" dxfId="1034" priority="1062"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2147">
-    <cfRule type="duplicateValues" dxfId="1033" priority="1041"/>
-    <cfRule type="duplicateValues" dxfId="1032" priority="1039"/>
-    <cfRule type="duplicateValues" dxfId="1031" priority="1038"/>
-    <cfRule type="duplicateValues" dxfId="1030" priority="1046"/>
-    <cfRule type="duplicateValues" dxfId="1029" priority="1047"/>
-    <cfRule type="duplicateValues" dxfId="1028" priority="1045"/>
-    <cfRule type="duplicateValues" dxfId="1027" priority="1044"/>
-    <cfRule type="duplicateValues" dxfId="1026" priority="1043"/>
-    <cfRule type="duplicateValues" dxfId="1025" priority="1037"/>
+  <conditionalFormatting sqref="A2147">
+    <cfRule type="duplicateValues" dxfId="1033" priority="1033"/>
+    <cfRule type="duplicateValues" dxfId="1032" priority="1034"/>
+    <cfRule type="duplicateValues" dxfId="1031" priority="1035"/>
+    <cfRule type="duplicateValues" dxfId="1030" priority="1036"/>
+    <cfRule type="duplicateValues" dxfId="1029" priority="1037"/>
+    <cfRule type="duplicateValues" dxfId="1028" priority="1038"/>
+    <cfRule type="duplicateValues" dxfId="1027" priority="1039"/>
+    <cfRule type="duplicateValues" dxfId="1026" priority="1040"/>
+    <cfRule type="duplicateValues" dxfId="1025" priority="1041"/>
     <cfRule type="duplicateValues" dxfId="1024" priority="1042"/>
-    <cfRule type="duplicateValues" dxfId="1023" priority="1035"/>
-    <cfRule type="duplicateValues" dxfId="1022" priority="1034"/>
-    <cfRule type="duplicateValues" dxfId="1021" priority="1033"/>
-    <cfRule type="duplicateValues" dxfId="1020" priority="1040"/>
-    <cfRule type="duplicateValues" dxfId="1019" priority="1036"/>
+    <cfRule type="duplicateValues" dxfId="1023" priority="1043"/>
+    <cfRule type="duplicateValues" dxfId="1022" priority="1044"/>
+    <cfRule type="duplicateValues" dxfId="1021" priority="1045"/>
+    <cfRule type="duplicateValues" dxfId="1020" priority="1046"/>
+    <cfRule type="duplicateValues" dxfId="1019" priority="1047"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2151">
+  <conditionalFormatting sqref="A2151">
     <cfRule type="duplicateValues" dxfId="1018" priority="1025"/>
-    <cfRule type="duplicateValues" dxfId="1017" priority="1028"/>
-    <cfRule type="duplicateValues" dxfId="1016" priority="1029"/>
-    <cfRule type="duplicateValues" dxfId="1015" priority="1030"/>
-    <cfRule type="duplicateValues" dxfId="1014" priority="1031"/>
-    <cfRule type="duplicateValues" dxfId="1013" priority="1032"/>
-    <cfRule type="duplicateValues" dxfId="1012" priority="1027"/>
-    <cfRule type="duplicateValues" dxfId="1011" priority="1026"/>
+    <cfRule type="duplicateValues" dxfId="1017" priority="1026"/>
+    <cfRule type="duplicateValues" dxfId="1016" priority="1027"/>
+    <cfRule type="duplicateValues" dxfId="1015" priority="1028"/>
+    <cfRule type="duplicateValues" dxfId="1014" priority="1029"/>
+    <cfRule type="duplicateValues" dxfId="1013" priority="1030"/>
+    <cfRule type="duplicateValues" dxfId="1012" priority="1031"/>
+    <cfRule type="duplicateValues" dxfId="1011" priority="1032"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2152">
-    <cfRule type="duplicateValues" dxfId="1010" priority="1024"/>
-    <cfRule type="duplicateValues" dxfId="1009" priority="1023"/>
-    <cfRule type="duplicateValues" dxfId="1008" priority="1022"/>
-    <cfRule type="duplicateValues" dxfId="1007" priority="1021"/>
-    <cfRule type="duplicateValues" dxfId="1006" priority="1020"/>
-    <cfRule type="duplicateValues" dxfId="1005" priority="1019"/>
-    <cfRule type="duplicateValues" dxfId="1004" priority="1018"/>
-    <cfRule type="duplicateValues" dxfId="1003" priority="1017"/>
+  <conditionalFormatting sqref="A2152">
+    <cfRule type="duplicateValues" dxfId="1010" priority="1017"/>
+    <cfRule type="duplicateValues" dxfId="1009" priority="1018"/>
+    <cfRule type="duplicateValues" dxfId="1008" priority="1019"/>
+    <cfRule type="duplicateValues" dxfId="1007" priority="1020"/>
+    <cfRule type="duplicateValues" dxfId="1006" priority="1021"/>
+    <cfRule type="duplicateValues" dxfId="1005" priority="1022"/>
+    <cfRule type="duplicateValues" dxfId="1004" priority="1023"/>
+    <cfRule type="duplicateValues" dxfId="1003" priority="1024"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2155">
-    <cfRule type="duplicateValues" dxfId="1002" priority="1009"/>
+  <conditionalFormatting sqref="A2155">
+    <cfRule type="duplicateValues" dxfId="1002" priority="1007"/>
     <cfRule type="duplicateValues" dxfId="1001" priority="1008"/>
-    <cfRule type="duplicateValues" dxfId="1000" priority="1007"/>
-    <cfRule type="duplicateValues" dxfId="999" priority="1015"/>
-    <cfRule type="duplicateValues" dxfId="998" priority="1014"/>
-    <cfRule type="duplicateValues" dxfId="997" priority="1013"/>
-    <cfRule type="duplicateValues" dxfId="996" priority="1012"/>
-    <cfRule type="duplicateValues" dxfId="995" priority="1011"/>
-    <cfRule type="duplicateValues" dxfId="994" priority="1010"/>
+    <cfRule type="duplicateValues" dxfId="1000" priority="1009"/>
+    <cfRule type="duplicateValues" dxfId="999" priority="1010"/>
+    <cfRule type="duplicateValues" dxfId="998" priority="1011"/>
+    <cfRule type="duplicateValues" dxfId="997" priority="1012"/>
+    <cfRule type="duplicateValues" dxfId="996" priority="1013"/>
+    <cfRule type="duplicateValues" dxfId="995" priority="1014"/>
+    <cfRule type="duplicateValues" dxfId="994" priority="1015"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2181">
-    <cfRule type="duplicateValues" dxfId="993" priority="1003"/>
-    <cfRule type="duplicateValues" dxfId="992" priority="1004"/>
-    <cfRule type="duplicateValues" dxfId="991" priority="1002"/>
-    <cfRule type="duplicateValues" dxfId="990" priority="1001"/>
-    <cfRule type="duplicateValues" dxfId="989" priority="1000"/>
+  <conditionalFormatting sqref="A2181">
+    <cfRule type="duplicateValues" dxfId="993" priority="994"/>
+    <cfRule type="duplicateValues" dxfId="992" priority="995"/>
+    <cfRule type="duplicateValues" dxfId="991" priority="996"/>
+    <cfRule type="duplicateValues" dxfId="990" priority="997"/>
+    <cfRule type="duplicateValues" dxfId="989" priority="998"/>
     <cfRule type="duplicateValues" dxfId="988" priority="999"/>
-    <cfRule type="duplicateValues" dxfId="987" priority="998"/>
-    <cfRule type="duplicateValues" dxfId="986" priority="997"/>
-    <cfRule type="duplicateValues" dxfId="985" priority="996"/>
-    <cfRule type="duplicateValues" dxfId="984" priority="995"/>
-    <cfRule type="duplicateValues" dxfId="983" priority="994"/>
+    <cfRule type="duplicateValues" dxfId="987" priority="1000"/>
+    <cfRule type="duplicateValues" dxfId="986" priority="1001"/>
+    <cfRule type="duplicateValues" dxfId="985" priority="1002"/>
+    <cfRule type="duplicateValues" dxfId="984" priority="1003"/>
+    <cfRule type="duplicateValues" dxfId="983" priority="1004"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2194">
-    <cfRule type="duplicateValues" dxfId="982" priority="977"/>
-    <cfRule type="duplicateValues" dxfId="981" priority="976"/>
-    <cfRule type="duplicateValues" dxfId="980" priority="975"/>
-    <cfRule type="duplicateValues" dxfId="979" priority="974"/>
-    <cfRule type="duplicateValues" dxfId="978" priority="973"/>
-    <cfRule type="duplicateValues" dxfId="977" priority="972"/>
-    <cfRule type="duplicateValues" dxfId="976" priority="982"/>
-    <cfRule type="duplicateValues" dxfId="975" priority="978"/>
-    <cfRule type="duplicateValues" dxfId="974" priority="979"/>
-    <cfRule type="duplicateValues" dxfId="973" priority="980"/>
-    <cfRule type="duplicateValues" dxfId="972" priority="981"/>
+  <conditionalFormatting sqref="A2194">
+    <cfRule type="duplicateValues" dxfId="982" priority="972"/>
+    <cfRule type="duplicateValues" dxfId="981" priority="973"/>
+    <cfRule type="duplicateValues" dxfId="980" priority="974"/>
+    <cfRule type="duplicateValues" dxfId="979" priority="975"/>
+    <cfRule type="duplicateValues" dxfId="978" priority="976"/>
+    <cfRule type="duplicateValues" dxfId="977" priority="977"/>
+    <cfRule type="duplicateValues" dxfId="976" priority="978"/>
+    <cfRule type="duplicateValues" dxfId="975" priority="979"/>
+    <cfRule type="duplicateValues" dxfId="974" priority="980"/>
+    <cfRule type="duplicateValues" dxfId="973" priority="981"/>
+    <cfRule type="duplicateValues" dxfId="972" priority="982"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2195">
-    <cfRule type="duplicateValues" dxfId="971" priority="971"/>
-    <cfRule type="duplicateValues" dxfId="970" priority="970"/>
-    <cfRule type="duplicateValues" dxfId="969" priority="969"/>
-    <cfRule type="duplicateValues" dxfId="968" priority="968"/>
-    <cfRule type="duplicateValues" dxfId="967" priority="967"/>
+  <conditionalFormatting sqref="A2195">
+    <cfRule type="duplicateValues" dxfId="971" priority="961"/>
+    <cfRule type="duplicateValues" dxfId="970" priority="962"/>
+    <cfRule type="duplicateValues" dxfId="969" priority="963"/>
+    <cfRule type="duplicateValues" dxfId="968" priority="964"/>
+    <cfRule type="duplicateValues" dxfId="967" priority="965"/>
     <cfRule type="duplicateValues" dxfId="966" priority="966"/>
-    <cfRule type="duplicateValues" dxfId="965" priority="964"/>
-    <cfRule type="duplicateValues" dxfId="964" priority="963"/>
-    <cfRule type="duplicateValues" dxfId="963" priority="962"/>
-    <cfRule type="duplicateValues" dxfId="962" priority="961"/>
-    <cfRule type="duplicateValues" dxfId="961" priority="965"/>
+    <cfRule type="duplicateValues" dxfId="965" priority="967"/>
+    <cfRule type="duplicateValues" dxfId="964" priority="968"/>
+    <cfRule type="duplicateValues" dxfId="963" priority="969"/>
+    <cfRule type="duplicateValues" dxfId="962" priority="970"/>
+    <cfRule type="duplicateValues" dxfId="961" priority="971"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2196">
-    <cfRule type="duplicateValues" dxfId="960" priority="1193"/>
-    <cfRule type="duplicateValues" dxfId="959" priority="1195"/>
+  <conditionalFormatting sqref="A2196">
+    <cfRule type="duplicateValues" dxfId="960" priority="1190"/>
+    <cfRule type="duplicateValues" dxfId="959" priority="1191"/>
     <cfRule type="duplicateValues" dxfId="958" priority="1192"/>
-    <cfRule type="duplicateValues" dxfId="957" priority="1191"/>
+    <cfRule type="duplicateValues" dxfId="957" priority="1193"/>
     <cfRule type="duplicateValues" dxfId="956" priority="1194"/>
-    <cfRule type="duplicateValues" dxfId="955" priority="1190"/>
+    <cfRule type="duplicateValues" dxfId="955" priority="1195"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2197">
-    <cfRule type="duplicateValues" dxfId="954" priority="960"/>
-    <cfRule type="duplicateValues" dxfId="953" priority="959"/>
-    <cfRule type="duplicateValues" dxfId="952" priority="953"/>
-    <cfRule type="duplicateValues" dxfId="951" priority="954"/>
-    <cfRule type="duplicateValues" dxfId="950" priority="951"/>
-    <cfRule type="duplicateValues" dxfId="949" priority="950"/>
-    <cfRule type="duplicateValues" dxfId="948" priority="952"/>
-    <cfRule type="duplicateValues" dxfId="947" priority="955"/>
-    <cfRule type="duplicateValues" dxfId="946" priority="956"/>
-    <cfRule type="duplicateValues" dxfId="945" priority="957"/>
-    <cfRule type="duplicateValues" dxfId="944" priority="958"/>
+  <conditionalFormatting sqref="A2197">
+    <cfRule type="duplicateValues" dxfId="954" priority="950"/>
+    <cfRule type="duplicateValues" dxfId="953" priority="951"/>
+    <cfRule type="duplicateValues" dxfId="952" priority="952"/>
+    <cfRule type="duplicateValues" dxfId="951" priority="953"/>
+    <cfRule type="duplicateValues" dxfId="950" priority="954"/>
+    <cfRule type="duplicateValues" dxfId="949" priority="955"/>
+    <cfRule type="duplicateValues" dxfId="948" priority="956"/>
+    <cfRule type="duplicateValues" dxfId="947" priority="957"/>
+    <cfRule type="duplicateValues" dxfId="946" priority="958"/>
+    <cfRule type="duplicateValues" dxfId="945" priority="959"/>
+    <cfRule type="duplicateValues" dxfId="944" priority="960"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2208">
-    <cfRule type="duplicateValues" dxfId="943" priority="947"/>
-    <cfRule type="duplicateValues" dxfId="942" priority="946"/>
-    <cfRule type="duplicateValues" dxfId="941" priority="945"/>
-    <cfRule type="duplicateValues" dxfId="940" priority="944"/>
+  <conditionalFormatting sqref="A2208">
+    <cfRule type="duplicateValues" dxfId="943" priority="939"/>
+    <cfRule type="duplicateValues" dxfId="942" priority="940"/>
+    <cfRule type="duplicateValues" dxfId="941" priority="941"/>
+    <cfRule type="duplicateValues" dxfId="940" priority="942"/>
     <cfRule type="duplicateValues" dxfId="939" priority="943"/>
-    <cfRule type="duplicateValues" dxfId="938" priority="942"/>
-    <cfRule type="duplicateValues" dxfId="937" priority="941"/>
-    <cfRule type="duplicateValues" dxfId="936" priority="939"/>
-    <cfRule type="duplicateValues" dxfId="935" priority="949"/>
+    <cfRule type="duplicateValues" dxfId="938" priority="944"/>
+    <cfRule type="duplicateValues" dxfId="937" priority="945"/>
+    <cfRule type="duplicateValues" dxfId="936" priority="946"/>
+    <cfRule type="duplicateValues" dxfId="935" priority="947"/>
     <cfRule type="duplicateValues" dxfId="934" priority="948"/>
-    <cfRule type="duplicateValues" dxfId="933" priority="940"/>
+    <cfRule type="duplicateValues" dxfId="933" priority="949"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2214">
+  <conditionalFormatting sqref="A2214">
     <cfRule type="duplicateValues" dxfId="932" priority="926"/>
-    <cfRule type="duplicateValues" dxfId="931" priority="936"/>
-    <cfRule type="duplicateValues" dxfId="930" priority="927"/>
-    <cfRule type="duplicateValues" dxfId="929" priority="935"/>
-    <cfRule type="duplicateValues" dxfId="928" priority="934"/>
-    <cfRule type="duplicateValues" dxfId="927" priority="933"/>
+    <cfRule type="duplicateValues" dxfId="931" priority="927"/>
+    <cfRule type="duplicateValues" dxfId="930" priority="928"/>
+    <cfRule type="duplicateValues" dxfId="929" priority="929"/>
+    <cfRule type="duplicateValues" dxfId="928" priority="930"/>
+    <cfRule type="duplicateValues" dxfId="927" priority="931"/>
     <cfRule type="duplicateValues" dxfId="926" priority="932"/>
-    <cfRule type="duplicateValues" dxfId="925" priority="931"/>
-    <cfRule type="duplicateValues" dxfId="924" priority="930"/>
-    <cfRule type="duplicateValues" dxfId="923" priority="929"/>
-    <cfRule type="duplicateValues" dxfId="922" priority="928"/>
+    <cfRule type="duplicateValues" dxfId="925" priority="933"/>
+    <cfRule type="duplicateValues" dxfId="924" priority="934"/>
+    <cfRule type="duplicateValues" dxfId="923" priority="935"/>
+    <cfRule type="duplicateValues" dxfId="922" priority="936"/>
     <cfRule type="duplicateValues" dxfId="921" priority="937"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2215">
+  <conditionalFormatting sqref="A2215">
     <cfRule type="duplicateValues" dxfId="920" priority="914"/>
-    <cfRule type="duplicateValues" dxfId="919" priority="925"/>
-    <cfRule type="duplicateValues" dxfId="918" priority="924"/>
-    <cfRule type="duplicateValues" dxfId="917" priority="923"/>
-    <cfRule type="duplicateValues" dxfId="916" priority="922"/>
-    <cfRule type="duplicateValues" dxfId="915" priority="921"/>
+    <cfRule type="duplicateValues" dxfId="919" priority="915"/>
+    <cfRule type="duplicateValues" dxfId="918" priority="916"/>
+    <cfRule type="duplicateValues" dxfId="917" priority="917"/>
+    <cfRule type="duplicateValues" dxfId="916" priority="918"/>
+    <cfRule type="duplicateValues" dxfId="915" priority="919"/>
     <cfRule type="duplicateValues" dxfId="914" priority="920"/>
-    <cfRule type="duplicateValues" dxfId="913" priority="919"/>
-    <cfRule type="duplicateValues" dxfId="912" priority="918"/>
-    <cfRule type="duplicateValues" dxfId="911" priority="917"/>
-    <cfRule type="duplicateValues" dxfId="910" priority="916"/>
-    <cfRule type="duplicateValues" dxfId="909" priority="915"/>
+    <cfRule type="duplicateValues" dxfId="913" priority="921"/>
+    <cfRule type="duplicateValues" dxfId="912" priority="922"/>
+    <cfRule type="duplicateValues" dxfId="911" priority="923"/>
+    <cfRule type="duplicateValues" dxfId="910" priority="924"/>
+    <cfRule type="duplicateValues" dxfId="909" priority="925"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2216">
-    <cfRule type="duplicateValues" dxfId="908" priority="912"/>
-    <cfRule type="duplicateValues" dxfId="907" priority="911"/>
-    <cfRule type="duplicateValues" dxfId="906" priority="910"/>
-    <cfRule type="duplicateValues" dxfId="905" priority="908"/>
-    <cfRule type="duplicateValues" dxfId="904" priority="907"/>
-    <cfRule type="duplicateValues" dxfId="903" priority="906"/>
-    <cfRule type="duplicateValues" dxfId="902" priority="905"/>
-    <cfRule type="duplicateValues" dxfId="901" priority="904"/>
-    <cfRule type="duplicateValues" dxfId="900" priority="903"/>
-    <cfRule type="duplicateValues" dxfId="899" priority="902"/>
-    <cfRule type="duplicateValues" dxfId="898" priority="901"/>
-    <cfRule type="duplicateValues" dxfId="897" priority="900"/>
-    <cfRule type="duplicateValues" dxfId="896" priority="909"/>
+  <conditionalFormatting sqref="A2216">
+    <cfRule type="duplicateValues" dxfId="908" priority="900"/>
+    <cfRule type="duplicateValues" dxfId="907" priority="901"/>
+    <cfRule type="duplicateValues" dxfId="906" priority="902"/>
+    <cfRule type="duplicateValues" dxfId="905" priority="903"/>
+    <cfRule type="duplicateValues" dxfId="904" priority="904"/>
+    <cfRule type="duplicateValues" dxfId="903" priority="905"/>
+    <cfRule type="duplicateValues" dxfId="902" priority="906"/>
+    <cfRule type="duplicateValues" dxfId="901" priority="907"/>
+    <cfRule type="duplicateValues" dxfId="900" priority="908"/>
+    <cfRule type="duplicateValues" dxfId="899" priority="909"/>
+    <cfRule type="duplicateValues" dxfId="898" priority="910"/>
+    <cfRule type="duplicateValues" dxfId="897" priority="911"/>
+    <cfRule type="duplicateValues" dxfId="896" priority="912"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2217">
-    <cfRule type="duplicateValues" dxfId="895" priority="888"/>
-    <cfRule type="duplicateValues" dxfId="894" priority="887"/>
-    <cfRule type="duplicateValues" dxfId="893" priority="897"/>
-    <cfRule type="duplicateValues" dxfId="892" priority="899"/>
-    <cfRule type="duplicateValues" dxfId="891" priority="898"/>
-    <cfRule type="duplicateValues" dxfId="890" priority="896"/>
-    <cfRule type="duplicateValues" dxfId="889" priority="895"/>
+  <conditionalFormatting sqref="A2217">
+    <cfRule type="duplicateValues" dxfId="895" priority="887"/>
+    <cfRule type="duplicateValues" dxfId="894" priority="888"/>
+    <cfRule type="duplicateValues" dxfId="893" priority="889"/>
+    <cfRule type="duplicateValues" dxfId="892" priority="890"/>
+    <cfRule type="duplicateValues" dxfId="891" priority="891"/>
+    <cfRule type="duplicateValues" dxfId="890" priority="892"/>
+    <cfRule type="duplicateValues" dxfId="889" priority="893"/>
     <cfRule type="duplicateValues" dxfId="888" priority="894"/>
-    <cfRule type="duplicateValues" dxfId="887" priority="893"/>
-    <cfRule type="duplicateValues" dxfId="886" priority="892"/>
-    <cfRule type="duplicateValues" dxfId="885" priority="891"/>
-    <cfRule type="duplicateValues" dxfId="884" priority="890"/>
-    <cfRule type="duplicateValues" dxfId="883" priority="889"/>
+    <cfRule type="duplicateValues" dxfId="887" priority="895"/>
+    <cfRule type="duplicateValues" dxfId="886" priority="896"/>
+    <cfRule type="duplicateValues" dxfId="885" priority="897"/>
+    <cfRule type="duplicateValues" dxfId="884" priority="898"/>
+    <cfRule type="duplicateValues" dxfId="883" priority="899"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2218">
+  <conditionalFormatting sqref="A2218">
     <cfRule type="duplicateValues" dxfId="882" priority="861"/>
     <cfRule type="duplicateValues" dxfId="881" priority="862"/>
-    <cfRule type="duplicateValues" dxfId="880" priority="873"/>
-    <cfRule type="duplicateValues" dxfId="879" priority="872"/>
-    <cfRule type="duplicateValues" dxfId="878" priority="871"/>
-    <cfRule type="duplicateValues" dxfId="877" priority="870"/>
-    <cfRule type="duplicateValues" dxfId="876" priority="869"/>
+    <cfRule type="duplicateValues" dxfId="880" priority="863"/>
+    <cfRule type="duplicateValues" dxfId="879" priority="864"/>
+    <cfRule type="duplicateValues" dxfId="878" priority="865"/>
+    <cfRule type="duplicateValues" dxfId="877" priority="866"/>
+    <cfRule type="duplicateValues" dxfId="876" priority="867"/>
     <cfRule type="duplicateValues" dxfId="875" priority="868"/>
-    <cfRule type="duplicateValues" dxfId="874" priority="867"/>
-    <cfRule type="duplicateValues" dxfId="873" priority="866"/>
-    <cfRule type="duplicateValues" dxfId="872" priority="865"/>
-    <cfRule type="duplicateValues" dxfId="871" priority="864"/>
-    <cfRule type="duplicateValues" dxfId="870" priority="863"/>
+    <cfRule type="duplicateValues" dxfId="874" priority="869"/>
+    <cfRule type="duplicateValues" dxfId="873" priority="870"/>
+    <cfRule type="duplicateValues" dxfId="872" priority="871"/>
+    <cfRule type="duplicateValues" dxfId="871" priority="872"/>
+    <cfRule type="duplicateValues" dxfId="870" priority="873"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2219">
-    <cfRule type="duplicateValues" dxfId="869" priority="849"/>
-    <cfRule type="duplicateValues" dxfId="868" priority="848"/>
-    <cfRule type="duplicateValues" dxfId="867" priority="860"/>
-    <cfRule type="duplicateValues" dxfId="866" priority="859"/>
-    <cfRule type="duplicateValues" dxfId="865" priority="858"/>
-    <cfRule type="duplicateValues" dxfId="864" priority="857"/>
-    <cfRule type="duplicateValues" dxfId="863" priority="856"/>
+  <conditionalFormatting sqref="A2219">
+    <cfRule type="duplicateValues" dxfId="869" priority="848"/>
+    <cfRule type="duplicateValues" dxfId="868" priority="849"/>
+    <cfRule type="duplicateValues" dxfId="867" priority="850"/>
+    <cfRule type="duplicateValues" dxfId="866" priority="851"/>
+    <cfRule type="duplicateValues" dxfId="865" priority="852"/>
+    <cfRule type="duplicateValues" dxfId="864" priority="853"/>
+    <cfRule type="duplicateValues" dxfId="863" priority="854"/>
     <cfRule type="duplicateValues" dxfId="862" priority="855"/>
-    <cfRule type="duplicateValues" dxfId="861" priority="854"/>
-    <cfRule type="duplicateValues" dxfId="860" priority="853"/>
-    <cfRule type="duplicateValues" dxfId="859" priority="852"/>
-    <cfRule type="duplicateValues" dxfId="858" priority="851"/>
-    <cfRule type="duplicateValues" dxfId="857" priority="850"/>
+    <cfRule type="duplicateValues" dxfId="861" priority="856"/>
+    <cfRule type="duplicateValues" dxfId="860" priority="857"/>
+    <cfRule type="duplicateValues" dxfId="859" priority="858"/>
+    <cfRule type="duplicateValues" dxfId="858" priority="859"/>
+    <cfRule type="duplicateValues" dxfId="857" priority="860"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2220">
-    <cfRule type="duplicateValues" dxfId="856" priority="841"/>
-    <cfRule type="duplicateValues" dxfId="855" priority="847"/>
-    <cfRule type="duplicateValues" dxfId="854" priority="846"/>
-    <cfRule type="duplicateValues" dxfId="853" priority="845"/>
-    <cfRule type="duplicateValues" dxfId="852" priority="844"/>
-    <cfRule type="duplicateValues" dxfId="851" priority="843"/>
-    <cfRule type="duplicateValues" dxfId="850" priority="842"/>
-    <cfRule type="duplicateValues" dxfId="849" priority="840"/>
-    <cfRule type="duplicateValues" dxfId="848" priority="839"/>
-    <cfRule type="duplicateValues" dxfId="847" priority="838"/>
-    <cfRule type="duplicateValues" dxfId="846" priority="837"/>
-    <cfRule type="duplicateValues" dxfId="845" priority="836"/>
-    <cfRule type="duplicateValues" dxfId="844" priority="835"/>
+  <conditionalFormatting sqref="A2220">
+    <cfRule type="duplicateValues" dxfId="856" priority="835"/>
+    <cfRule type="duplicateValues" dxfId="855" priority="836"/>
+    <cfRule type="duplicateValues" dxfId="854" priority="837"/>
+    <cfRule type="duplicateValues" dxfId="853" priority="838"/>
+    <cfRule type="duplicateValues" dxfId="852" priority="839"/>
+    <cfRule type="duplicateValues" dxfId="851" priority="840"/>
+    <cfRule type="duplicateValues" dxfId="850" priority="841"/>
+    <cfRule type="duplicateValues" dxfId="849" priority="842"/>
+    <cfRule type="duplicateValues" dxfId="848" priority="843"/>
+    <cfRule type="duplicateValues" dxfId="847" priority="844"/>
+    <cfRule type="duplicateValues" dxfId="846" priority="845"/>
+    <cfRule type="duplicateValues" dxfId="845" priority="846"/>
+    <cfRule type="duplicateValues" dxfId="844" priority="847"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2224">
-    <cfRule type="duplicateValues" dxfId="843" priority="823"/>
-    <cfRule type="duplicateValues" dxfId="842" priority="822"/>
-    <cfRule type="duplicateValues" dxfId="841" priority="834"/>
-    <cfRule type="duplicateValues" dxfId="840" priority="833"/>
-    <cfRule type="duplicateValues" dxfId="839" priority="832"/>
-    <cfRule type="duplicateValues" dxfId="838" priority="831"/>
-    <cfRule type="duplicateValues" dxfId="837" priority="830"/>
+  <conditionalFormatting sqref="A2224">
+    <cfRule type="duplicateValues" dxfId="843" priority="822"/>
+    <cfRule type="duplicateValues" dxfId="842" priority="823"/>
+    <cfRule type="duplicateValues" dxfId="841" priority="824"/>
+    <cfRule type="duplicateValues" dxfId="840" priority="825"/>
+    <cfRule type="duplicateValues" dxfId="839" priority="826"/>
+    <cfRule type="duplicateValues" dxfId="838" priority="827"/>
+    <cfRule type="duplicateValues" dxfId="837" priority="828"/>
     <cfRule type="duplicateValues" dxfId="836" priority="829"/>
-    <cfRule type="duplicateValues" dxfId="835" priority="828"/>
-    <cfRule type="duplicateValues" dxfId="834" priority="827"/>
-    <cfRule type="duplicateValues" dxfId="833" priority="826"/>
-    <cfRule type="duplicateValues" dxfId="832" priority="825"/>
-    <cfRule type="duplicateValues" dxfId="831" priority="824"/>
+    <cfRule type="duplicateValues" dxfId="835" priority="830"/>
+    <cfRule type="duplicateValues" dxfId="834" priority="831"/>
+    <cfRule type="duplicateValues" dxfId="833" priority="832"/>
+    <cfRule type="duplicateValues" dxfId="832" priority="833"/>
+    <cfRule type="duplicateValues" dxfId="831" priority="834"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2225">
-    <cfRule type="duplicateValues" dxfId="830" priority="810"/>
-    <cfRule type="duplicateValues" dxfId="829" priority="809"/>
-    <cfRule type="duplicateValues" dxfId="828" priority="821"/>
-    <cfRule type="duplicateValues" dxfId="827" priority="820"/>
-    <cfRule type="duplicateValues" dxfId="826" priority="819"/>
-    <cfRule type="duplicateValues" dxfId="825" priority="818"/>
-    <cfRule type="duplicateValues" dxfId="824" priority="817"/>
+  <conditionalFormatting sqref="A2225">
+    <cfRule type="duplicateValues" dxfId="830" priority="809"/>
+    <cfRule type="duplicateValues" dxfId="829" priority="810"/>
+    <cfRule type="duplicateValues" dxfId="828" priority="811"/>
+    <cfRule type="duplicateValues" dxfId="827" priority="812"/>
+    <cfRule type="duplicateValues" dxfId="826" priority="813"/>
+    <cfRule type="duplicateValues" dxfId="825" priority="814"/>
+    <cfRule type="duplicateValues" dxfId="824" priority="815"/>
     <cfRule type="duplicateValues" dxfId="823" priority="816"/>
-    <cfRule type="duplicateValues" dxfId="822" priority="815"/>
-    <cfRule type="duplicateValues" dxfId="821" priority="814"/>
-    <cfRule type="duplicateValues" dxfId="820" priority="813"/>
-    <cfRule type="duplicateValues" dxfId="819" priority="812"/>
-    <cfRule type="duplicateValues" dxfId="818" priority="811"/>
+    <cfRule type="duplicateValues" dxfId="822" priority="817"/>
+    <cfRule type="duplicateValues" dxfId="821" priority="818"/>
+    <cfRule type="duplicateValues" dxfId="820" priority="819"/>
+    <cfRule type="duplicateValues" dxfId="819" priority="820"/>
+    <cfRule type="duplicateValues" dxfId="818" priority="821"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2226">
-    <cfRule type="duplicateValues" dxfId="817" priority="804"/>
-    <cfRule type="duplicateValues" dxfId="816" priority="807"/>
-    <cfRule type="duplicateValues" dxfId="815" priority="808"/>
-    <cfRule type="duplicateValues" dxfId="814" priority="797"/>
-    <cfRule type="duplicateValues" dxfId="813" priority="806"/>
-    <cfRule type="duplicateValues" dxfId="812" priority="805"/>
-    <cfRule type="duplicateValues" dxfId="811" priority="798"/>
+  <conditionalFormatting sqref="A2226">
+    <cfRule type="duplicateValues" dxfId="817" priority="796"/>
+    <cfRule type="duplicateValues" dxfId="816" priority="797"/>
+    <cfRule type="duplicateValues" dxfId="815" priority="798"/>
+    <cfRule type="duplicateValues" dxfId="814" priority="799"/>
+    <cfRule type="duplicateValues" dxfId="813" priority="800"/>
+    <cfRule type="duplicateValues" dxfId="812" priority="801"/>
+    <cfRule type="duplicateValues" dxfId="811" priority="802"/>
     <cfRule type="duplicateValues" dxfId="810" priority="803"/>
-    <cfRule type="duplicateValues" dxfId="809" priority="802"/>
-    <cfRule type="duplicateValues" dxfId="808" priority="801"/>
-    <cfRule type="duplicateValues" dxfId="807" priority="800"/>
-    <cfRule type="duplicateValues" dxfId="806" priority="799"/>
-    <cfRule type="duplicateValues" dxfId="805" priority="796"/>
+    <cfRule type="duplicateValues" dxfId="809" priority="804"/>
+    <cfRule type="duplicateValues" dxfId="808" priority="805"/>
+    <cfRule type="duplicateValues" dxfId="807" priority="806"/>
+    <cfRule type="duplicateValues" dxfId="806" priority="807"/>
+    <cfRule type="duplicateValues" dxfId="805" priority="808"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2227">
-    <cfRule type="duplicateValues" dxfId="804" priority="784"/>
-    <cfRule type="duplicateValues" dxfId="803" priority="783"/>
-    <cfRule type="duplicateValues" dxfId="802" priority="795"/>
-    <cfRule type="duplicateValues" dxfId="801" priority="794"/>
-    <cfRule type="duplicateValues" dxfId="800" priority="793"/>
-    <cfRule type="duplicateValues" dxfId="799" priority="792"/>
-    <cfRule type="duplicateValues" dxfId="798" priority="791"/>
+  <conditionalFormatting sqref="A2227">
+    <cfRule type="duplicateValues" dxfId="804" priority="783"/>
+    <cfRule type="duplicateValues" dxfId="803" priority="784"/>
+    <cfRule type="duplicateValues" dxfId="802" priority="785"/>
+    <cfRule type="duplicateValues" dxfId="801" priority="786"/>
+    <cfRule type="duplicateValues" dxfId="800" priority="787"/>
+    <cfRule type="duplicateValues" dxfId="799" priority="788"/>
+    <cfRule type="duplicateValues" dxfId="798" priority="789"/>
     <cfRule type="duplicateValues" dxfId="797" priority="790"/>
-    <cfRule type="duplicateValues" dxfId="796" priority="789"/>
-    <cfRule type="duplicateValues" dxfId="795" priority="788"/>
-    <cfRule type="duplicateValues" dxfId="794" priority="787"/>
-    <cfRule type="duplicateValues" dxfId="793" priority="786"/>
-    <cfRule type="duplicateValues" dxfId="792" priority="785"/>
+    <cfRule type="duplicateValues" dxfId="796" priority="791"/>
+    <cfRule type="duplicateValues" dxfId="795" priority="792"/>
+    <cfRule type="duplicateValues" dxfId="794" priority="793"/>
+    <cfRule type="duplicateValues" dxfId="793" priority="794"/>
+    <cfRule type="duplicateValues" dxfId="792" priority="795"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2228">
-    <cfRule type="duplicateValues" dxfId="791" priority="782"/>
-    <cfRule type="duplicateValues" dxfId="790" priority="781"/>
-    <cfRule type="duplicateValues" dxfId="789" priority="780"/>
-    <cfRule type="duplicateValues" dxfId="788" priority="779"/>
-    <cfRule type="duplicateValues" dxfId="787" priority="778"/>
-    <cfRule type="duplicateValues" dxfId="786" priority="777"/>
+  <conditionalFormatting sqref="A2228">
+    <cfRule type="duplicateValues" dxfId="791" priority="770"/>
+    <cfRule type="duplicateValues" dxfId="790" priority="771"/>
+    <cfRule type="duplicateValues" dxfId="789" priority="772"/>
+    <cfRule type="duplicateValues" dxfId="788" priority="773"/>
+    <cfRule type="duplicateValues" dxfId="787" priority="774"/>
+    <cfRule type="duplicateValues" dxfId="786" priority="775"/>
     <cfRule type="duplicateValues" dxfId="785" priority="776"/>
-    <cfRule type="duplicateValues" dxfId="784" priority="775"/>
-    <cfRule type="duplicateValues" dxfId="783" priority="774"/>
-    <cfRule type="duplicateValues" dxfId="782" priority="773"/>
-    <cfRule type="duplicateValues" dxfId="781" priority="772"/>
-    <cfRule type="duplicateValues" dxfId="780" priority="771"/>
-    <cfRule type="duplicateValues" dxfId="779" priority="770"/>
+    <cfRule type="duplicateValues" dxfId="784" priority="777"/>
+    <cfRule type="duplicateValues" dxfId="783" priority="778"/>
+    <cfRule type="duplicateValues" dxfId="782" priority="779"/>
+    <cfRule type="duplicateValues" dxfId="781" priority="780"/>
+    <cfRule type="duplicateValues" dxfId="780" priority="781"/>
+    <cfRule type="duplicateValues" dxfId="779" priority="782"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2266">
+  <conditionalFormatting sqref="A2266">
     <cfRule type="duplicateValues" dxfId="778" priority="757"/>
     <cfRule type="duplicateValues" dxfId="777" priority="758"/>
-    <cfRule type="duplicateValues" dxfId="776" priority="769"/>
-    <cfRule type="duplicateValues" dxfId="775" priority="768"/>
-    <cfRule type="duplicateValues" dxfId="774" priority="767"/>
-    <cfRule type="duplicateValues" dxfId="773" priority="766"/>
-    <cfRule type="duplicateValues" dxfId="772" priority="765"/>
+    <cfRule type="duplicateValues" dxfId="776" priority="759"/>
+    <cfRule type="duplicateValues" dxfId="775" priority="760"/>
+    <cfRule type="duplicateValues" dxfId="774" priority="761"/>
+    <cfRule type="duplicateValues" dxfId="773" priority="762"/>
+    <cfRule type="duplicateValues" dxfId="772" priority="763"/>
     <cfRule type="duplicateValues" dxfId="771" priority="764"/>
-    <cfRule type="duplicateValues" dxfId="770" priority="763"/>
-    <cfRule type="duplicateValues" dxfId="769" priority="762"/>
-    <cfRule type="duplicateValues" dxfId="768" priority="761"/>
-    <cfRule type="duplicateValues" dxfId="767" priority="760"/>
-    <cfRule type="duplicateValues" dxfId="766" priority="759"/>
+    <cfRule type="duplicateValues" dxfId="770" priority="765"/>
+    <cfRule type="duplicateValues" dxfId="769" priority="766"/>
+    <cfRule type="duplicateValues" dxfId="768" priority="767"/>
+    <cfRule type="duplicateValues" dxfId="767" priority="768"/>
+    <cfRule type="duplicateValues" dxfId="766" priority="769"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2267">
+  <conditionalFormatting sqref="A2267">
     <cfRule type="duplicateValues" dxfId="765" priority="744"/>
-    <cfRule type="duplicateValues" dxfId="764" priority="747"/>
-    <cfRule type="duplicateValues" dxfId="763" priority="756"/>
-    <cfRule type="duplicateValues" dxfId="762" priority="755"/>
-    <cfRule type="duplicateValues" dxfId="761" priority="754"/>
-    <cfRule type="duplicateValues" dxfId="760" priority="753"/>
-    <cfRule type="duplicateValues" dxfId="759" priority="752"/>
+    <cfRule type="duplicateValues" dxfId="764" priority="745"/>
+    <cfRule type="duplicateValues" dxfId="763" priority="746"/>
+    <cfRule type="duplicateValues" dxfId="762" priority="747"/>
+    <cfRule type="duplicateValues" dxfId="761" priority="748"/>
+    <cfRule type="duplicateValues" dxfId="760" priority="749"/>
+    <cfRule type="duplicateValues" dxfId="759" priority="750"/>
     <cfRule type="duplicateValues" dxfId="758" priority="751"/>
-    <cfRule type="duplicateValues" dxfId="757" priority="750"/>
-    <cfRule type="duplicateValues" dxfId="756" priority="749"/>
-    <cfRule type="duplicateValues" dxfId="755" priority="748"/>
-    <cfRule type="duplicateValues" dxfId="754" priority="746"/>
-    <cfRule type="duplicateValues" dxfId="753" priority="745"/>
+    <cfRule type="duplicateValues" dxfId="757" priority="752"/>
+    <cfRule type="duplicateValues" dxfId="756" priority="753"/>
+    <cfRule type="duplicateValues" dxfId="755" priority="754"/>
+    <cfRule type="duplicateValues" dxfId="754" priority="755"/>
+    <cfRule type="duplicateValues" dxfId="753" priority="756"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2268">
-    <cfRule type="duplicateValues" dxfId="752" priority="737"/>
-    <cfRule type="duplicateValues" dxfId="751" priority="743"/>
-    <cfRule type="duplicateValues" dxfId="750" priority="742"/>
-    <cfRule type="duplicateValues" dxfId="749" priority="741"/>
-    <cfRule type="duplicateValues" dxfId="748" priority="740"/>
-    <cfRule type="duplicateValues" dxfId="747" priority="739"/>
-    <cfRule type="duplicateValues" dxfId="746" priority="738"/>
-    <cfRule type="duplicateValues" dxfId="745" priority="736"/>
-    <cfRule type="duplicateValues" dxfId="744" priority="735"/>
-    <cfRule type="duplicateValues" dxfId="743" priority="734"/>
-    <cfRule type="duplicateValues" dxfId="742" priority="733"/>
-    <cfRule type="duplicateValues" dxfId="741" priority="732"/>
-    <cfRule type="duplicateValues" dxfId="740" priority="731"/>
+  <conditionalFormatting sqref="A2268">
+    <cfRule type="duplicateValues" dxfId="752" priority="731"/>
+    <cfRule type="duplicateValues" dxfId="751" priority="732"/>
+    <cfRule type="duplicateValues" dxfId="750" priority="733"/>
+    <cfRule type="duplicateValues" dxfId="749" priority="734"/>
+    <cfRule type="duplicateValues" dxfId="748" priority="735"/>
+    <cfRule type="duplicateValues" dxfId="747" priority="736"/>
+    <cfRule type="duplicateValues" dxfId="746" priority="737"/>
+    <cfRule type="duplicateValues" dxfId="745" priority="738"/>
+    <cfRule type="duplicateValues" dxfId="744" priority="739"/>
+    <cfRule type="duplicateValues" dxfId="743" priority="740"/>
+    <cfRule type="duplicateValues" dxfId="742" priority="741"/>
+    <cfRule type="duplicateValues" dxfId="741" priority="742"/>
+    <cfRule type="duplicateValues" dxfId="740" priority="743"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2269">
-    <cfRule type="duplicateValues" dxfId="739" priority="719"/>
-    <cfRule type="duplicateValues" dxfId="738" priority="728"/>
-    <cfRule type="duplicateValues" dxfId="737" priority="730"/>
-    <cfRule type="duplicateValues" dxfId="736" priority="729"/>
-    <cfRule type="duplicateValues" dxfId="735" priority="718"/>
-    <cfRule type="duplicateValues" dxfId="734" priority="727"/>
-    <cfRule type="duplicateValues" dxfId="733" priority="726"/>
+  <conditionalFormatting sqref="A2269">
+    <cfRule type="duplicateValues" dxfId="739" priority="718"/>
+    <cfRule type="duplicateValues" dxfId="738" priority="719"/>
+    <cfRule type="duplicateValues" dxfId="737" priority="720"/>
+    <cfRule type="duplicateValues" dxfId="736" priority="721"/>
+    <cfRule type="duplicateValues" dxfId="735" priority="722"/>
+    <cfRule type="duplicateValues" dxfId="734" priority="723"/>
+    <cfRule type="duplicateValues" dxfId="733" priority="724"/>
     <cfRule type="duplicateValues" dxfId="732" priority="725"/>
-    <cfRule type="duplicateValues" dxfId="731" priority="724"/>
-    <cfRule type="duplicateValues" dxfId="730" priority="723"/>
-    <cfRule type="duplicateValues" dxfId="729" priority="722"/>
-    <cfRule type="duplicateValues" dxfId="728" priority="721"/>
-    <cfRule type="duplicateValues" dxfId="727" priority="720"/>
+    <cfRule type="duplicateValues" dxfId="731" priority="726"/>
+    <cfRule type="duplicateValues" dxfId="730" priority="727"/>
+    <cfRule type="duplicateValues" dxfId="729" priority="728"/>
+    <cfRule type="duplicateValues" dxfId="728" priority="729"/>
+    <cfRule type="duplicateValues" dxfId="727" priority="730"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2270">
+  <conditionalFormatting sqref="A2270">
     <cfRule type="duplicateValues" dxfId="726" priority="705"/>
-    <cfRule type="duplicateValues" dxfId="725" priority="711"/>
-    <cfRule type="duplicateValues" dxfId="724" priority="717"/>
-    <cfRule type="duplicateValues" dxfId="723" priority="716"/>
-    <cfRule type="duplicateValues" dxfId="722" priority="715"/>
-    <cfRule type="duplicateValues" dxfId="721" priority="714"/>
-    <cfRule type="duplicateValues" dxfId="720" priority="713"/>
+    <cfRule type="duplicateValues" dxfId="725" priority="706"/>
+    <cfRule type="duplicateValues" dxfId="724" priority="707"/>
+    <cfRule type="duplicateValues" dxfId="723" priority="708"/>
+    <cfRule type="duplicateValues" dxfId="722" priority="709"/>
+    <cfRule type="duplicateValues" dxfId="721" priority="710"/>
+    <cfRule type="duplicateValues" dxfId="720" priority="711"/>
     <cfRule type="duplicateValues" dxfId="719" priority="712"/>
-    <cfRule type="duplicateValues" dxfId="718" priority="710"/>
-    <cfRule type="duplicateValues" dxfId="717" priority="709"/>
-    <cfRule type="duplicateValues" dxfId="716" priority="708"/>
-    <cfRule type="duplicateValues" dxfId="715" priority="707"/>
-    <cfRule type="duplicateValues" dxfId="714" priority="706"/>
+    <cfRule type="duplicateValues" dxfId="718" priority="713"/>
+    <cfRule type="duplicateValues" dxfId="717" priority="714"/>
+    <cfRule type="duplicateValues" dxfId="716" priority="715"/>
+    <cfRule type="duplicateValues" dxfId="715" priority="716"/>
+    <cfRule type="duplicateValues" dxfId="714" priority="717"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2271">
-    <cfRule type="duplicateValues" dxfId="713" priority="704"/>
-    <cfRule type="duplicateValues" dxfId="712" priority="703"/>
-    <cfRule type="duplicateValues" dxfId="711" priority="702"/>
-    <cfRule type="duplicateValues" dxfId="710" priority="701"/>
-    <cfRule type="duplicateValues" dxfId="709" priority="700"/>
-    <cfRule type="duplicateValues" dxfId="708" priority="699"/>
+  <conditionalFormatting sqref="A2271">
+    <cfRule type="duplicateValues" dxfId="713" priority="692"/>
+    <cfRule type="duplicateValues" dxfId="712" priority="693"/>
+    <cfRule type="duplicateValues" dxfId="711" priority="694"/>
+    <cfRule type="duplicateValues" dxfId="710" priority="695"/>
+    <cfRule type="duplicateValues" dxfId="709" priority="696"/>
+    <cfRule type="duplicateValues" dxfId="708" priority="697"/>
     <cfRule type="duplicateValues" dxfId="707" priority="698"/>
-    <cfRule type="duplicateValues" dxfId="706" priority="697"/>
-    <cfRule type="duplicateValues" dxfId="705" priority="696"/>
-    <cfRule type="duplicateValues" dxfId="704" priority="695"/>
-    <cfRule type="duplicateValues" dxfId="703" priority="694"/>
-    <cfRule type="duplicateValues" dxfId="702" priority="693"/>
-    <cfRule type="duplicateValues" dxfId="701" priority="692"/>
+    <cfRule type="duplicateValues" dxfId="706" priority="699"/>
+    <cfRule type="duplicateValues" dxfId="705" priority="700"/>
+    <cfRule type="duplicateValues" dxfId="704" priority="701"/>
+    <cfRule type="duplicateValues" dxfId="703" priority="702"/>
+    <cfRule type="duplicateValues" dxfId="702" priority="703"/>
+    <cfRule type="duplicateValues" dxfId="701" priority="704"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2272">
-    <cfRule type="duplicateValues" dxfId="700" priority="680"/>
-    <cfRule type="duplicateValues" dxfId="699" priority="679"/>
-    <cfRule type="duplicateValues" dxfId="698" priority="691"/>
-    <cfRule type="duplicateValues" dxfId="697" priority="690"/>
-    <cfRule type="duplicateValues" dxfId="696" priority="689"/>
-    <cfRule type="duplicateValues" dxfId="695" priority="688"/>
-    <cfRule type="duplicateValues" dxfId="694" priority="687"/>
+  <conditionalFormatting sqref="A2272">
+    <cfRule type="duplicateValues" dxfId="700" priority="679"/>
+    <cfRule type="duplicateValues" dxfId="699" priority="680"/>
+    <cfRule type="duplicateValues" dxfId="698" priority="681"/>
+    <cfRule type="duplicateValues" dxfId="697" priority="682"/>
+    <cfRule type="duplicateValues" dxfId="696" priority="683"/>
+    <cfRule type="duplicateValues" dxfId="695" priority="684"/>
+    <cfRule type="duplicateValues" dxfId="694" priority="685"/>
     <cfRule type="duplicateValues" dxfId="693" priority="686"/>
-    <cfRule type="duplicateValues" dxfId="692" priority="685"/>
-    <cfRule type="duplicateValues" dxfId="691" priority="684"/>
-    <cfRule type="duplicateValues" dxfId="690" priority="683"/>
-    <cfRule type="duplicateValues" dxfId="689" priority="682"/>
-    <cfRule type="duplicateValues" dxfId="688" priority="681"/>
+    <cfRule type="duplicateValues" dxfId="692" priority="687"/>
+    <cfRule type="duplicateValues" dxfId="691" priority="688"/>
+    <cfRule type="duplicateValues" dxfId="690" priority="689"/>
+    <cfRule type="duplicateValues" dxfId="689" priority="690"/>
+    <cfRule type="duplicateValues" dxfId="688" priority="691"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2342">
-    <cfRule type="duplicateValues" dxfId="687" priority="667"/>
-    <cfRule type="duplicateValues" dxfId="686" priority="666"/>
-    <cfRule type="duplicateValues" dxfId="685" priority="678"/>
-    <cfRule type="duplicateValues" dxfId="684" priority="677"/>
-    <cfRule type="duplicateValues" dxfId="683" priority="676"/>
-    <cfRule type="duplicateValues" dxfId="682" priority="675"/>
-    <cfRule type="duplicateValues" dxfId="681" priority="674"/>
+  <conditionalFormatting sqref="A2342">
+    <cfRule type="duplicateValues" dxfId="687" priority="666"/>
+    <cfRule type="duplicateValues" dxfId="686" priority="667"/>
+    <cfRule type="duplicateValues" dxfId="685" priority="668"/>
+    <cfRule type="duplicateValues" dxfId="684" priority="669"/>
+    <cfRule type="duplicateValues" dxfId="683" priority="670"/>
+    <cfRule type="duplicateValues" dxfId="682" priority="671"/>
+    <cfRule type="duplicateValues" dxfId="681" priority="672"/>
     <cfRule type="duplicateValues" dxfId="680" priority="673"/>
-    <cfRule type="duplicateValues" dxfId="679" priority="672"/>
-    <cfRule type="duplicateValues" dxfId="678" priority="671"/>
-    <cfRule type="duplicateValues" dxfId="677" priority="670"/>
-    <cfRule type="duplicateValues" dxfId="676" priority="669"/>
-    <cfRule type="duplicateValues" dxfId="675" priority="668"/>
+    <cfRule type="duplicateValues" dxfId="679" priority="674"/>
+    <cfRule type="duplicateValues" dxfId="678" priority="675"/>
+    <cfRule type="duplicateValues" dxfId="677" priority="676"/>
+    <cfRule type="duplicateValues" dxfId="676" priority="677"/>
+    <cfRule type="duplicateValues" dxfId="675" priority="678"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2343:D2344">
-    <cfRule type="duplicateValues" dxfId="674" priority="659"/>
-    <cfRule type="duplicateValues" dxfId="673" priority="665"/>
-    <cfRule type="duplicateValues" dxfId="672" priority="664"/>
-    <cfRule type="duplicateValues" dxfId="671" priority="663"/>
-    <cfRule type="duplicateValues" dxfId="670" priority="662"/>
-    <cfRule type="duplicateValues" dxfId="669" priority="661"/>
-    <cfRule type="duplicateValues" dxfId="668" priority="660"/>
-    <cfRule type="duplicateValues" dxfId="667" priority="658"/>
-    <cfRule type="duplicateValues" dxfId="666" priority="657"/>
-    <cfRule type="duplicateValues" dxfId="665" priority="656"/>
-    <cfRule type="duplicateValues" dxfId="664" priority="655"/>
-    <cfRule type="duplicateValues" dxfId="663" priority="654"/>
-    <cfRule type="duplicateValues" dxfId="662" priority="653"/>
+  <conditionalFormatting sqref="A2343:A2344">
+    <cfRule type="duplicateValues" dxfId="674" priority="653"/>
+    <cfRule type="duplicateValues" dxfId="673" priority="654"/>
+    <cfRule type="duplicateValues" dxfId="672" priority="655"/>
+    <cfRule type="duplicateValues" dxfId="671" priority="656"/>
+    <cfRule type="duplicateValues" dxfId="670" priority="657"/>
+    <cfRule type="duplicateValues" dxfId="669" priority="658"/>
+    <cfRule type="duplicateValues" dxfId="668" priority="659"/>
+    <cfRule type="duplicateValues" dxfId="667" priority="660"/>
+    <cfRule type="duplicateValues" dxfId="666" priority="661"/>
+    <cfRule type="duplicateValues" dxfId="665" priority="662"/>
+    <cfRule type="duplicateValues" dxfId="664" priority="663"/>
+    <cfRule type="duplicateValues" dxfId="663" priority="664"/>
+    <cfRule type="duplicateValues" dxfId="662" priority="665"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2347">
-    <cfRule type="duplicateValues" dxfId="661" priority="641"/>
-    <cfRule type="duplicateValues" dxfId="660" priority="651"/>
-    <cfRule type="duplicateValues" dxfId="659" priority="652"/>
-    <cfRule type="duplicateValues" dxfId="658" priority="640"/>
-    <cfRule type="duplicateValues" dxfId="657" priority="650"/>
-    <cfRule type="duplicateValues" dxfId="656" priority="649"/>
-    <cfRule type="duplicateValues" dxfId="655" priority="648"/>
+  <conditionalFormatting sqref="A2347">
+    <cfRule type="duplicateValues" dxfId="661" priority="640"/>
+    <cfRule type="duplicateValues" dxfId="660" priority="641"/>
+    <cfRule type="duplicateValues" dxfId="659" priority="642"/>
+    <cfRule type="duplicateValues" dxfId="658" priority="643"/>
+    <cfRule type="duplicateValues" dxfId="657" priority="644"/>
+    <cfRule type="duplicateValues" dxfId="656" priority="645"/>
+    <cfRule type="duplicateValues" dxfId="655" priority="646"/>
     <cfRule type="duplicateValues" dxfId="654" priority="647"/>
-    <cfRule type="duplicateValues" dxfId="653" priority="646"/>
-    <cfRule type="duplicateValues" dxfId="652" priority="645"/>
-    <cfRule type="duplicateValues" dxfId="651" priority="644"/>
-    <cfRule type="duplicateValues" dxfId="650" priority="643"/>
-    <cfRule type="duplicateValues" dxfId="649" priority="642"/>
+    <cfRule type="duplicateValues" dxfId="653" priority="648"/>
+    <cfRule type="duplicateValues" dxfId="652" priority="649"/>
+    <cfRule type="duplicateValues" dxfId="651" priority="650"/>
+    <cfRule type="duplicateValues" dxfId="650" priority="651"/>
+    <cfRule type="duplicateValues" dxfId="649" priority="652"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2349">
-    <cfRule type="duplicateValues" dxfId="648" priority="628"/>
-    <cfRule type="duplicateValues" dxfId="647" priority="627"/>
-    <cfRule type="duplicateValues" dxfId="646" priority="639"/>
-    <cfRule type="duplicateValues" dxfId="645" priority="638"/>
-    <cfRule type="duplicateValues" dxfId="644" priority="637"/>
-    <cfRule type="duplicateValues" dxfId="643" priority="636"/>
-    <cfRule type="duplicateValues" dxfId="642" priority="635"/>
+  <conditionalFormatting sqref="A2349">
+    <cfRule type="duplicateValues" dxfId="648" priority="627"/>
+    <cfRule type="duplicateValues" dxfId="647" priority="628"/>
+    <cfRule type="duplicateValues" dxfId="646" priority="629"/>
+    <cfRule type="duplicateValues" dxfId="645" priority="630"/>
+    <cfRule type="duplicateValues" dxfId="644" priority="631"/>
+    <cfRule type="duplicateValues" dxfId="643" priority="632"/>
+    <cfRule type="duplicateValues" dxfId="642" priority="633"/>
     <cfRule type="duplicateValues" dxfId="641" priority="634"/>
-    <cfRule type="duplicateValues" dxfId="640" priority="633"/>
-    <cfRule type="duplicateValues" dxfId="639" priority="632"/>
-    <cfRule type="duplicateValues" dxfId="638" priority="631"/>
-    <cfRule type="duplicateValues" dxfId="637" priority="630"/>
-    <cfRule type="duplicateValues" dxfId="636" priority="629"/>
+    <cfRule type="duplicateValues" dxfId="640" priority="635"/>
+    <cfRule type="duplicateValues" dxfId="639" priority="636"/>
+    <cfRule type="duplicateValues" dxfId="638" priority="637"/>
+    <cfRule type="duplicateValues" dxfId="637" priority="638"/>
+    <cfRule type="duplicateValues" dxfId="636" priority="639"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2351">
-    <cfRule type="duplicateValues" dxfId="635" priority="626"/>
-    <cfRule type="duplicateValues" dxfId="634" priority="625"/>
-    <cfRule type="duplicateValues" dxfId="633" priority="624"/>
-    <cfRule type="duplicateValues" dxfId="632" priority="623"/>
-    <cfRule type="duplicateValues" dxfId="631" priority="622"/>
-    <cfRule type="duplicateValues" dxfId="630" priority="621"/>
+  <conditionalFormatting sqref="A2351">
+    <cfRule type="duplicateValues" dxfId="635" priority="614"/>
+    <cfRule type="duplicateValues" dxfId="634" priority="615"/>
+    <cfRule type="duplicateValues" dxfId="633" priority="616"/>
+    <cfRule type="duplicateValues" dxfId="632" priority="617"/>
+    <cfRule type="duplicateValues" dxfId="631" priority="618"/>
+    <cfRule type="duplicateValues" dxfId="630" priority="619"/>
     <cfRule type="duplicateValues" dxfId="629" priority="620"/>
-    <cfRule type="duplicateValues" dxfId="628" priority="619"/>
-    <cfRule type="duplicateValues" dxfId="627" priority="618"/>
-    <cfRule type="duplicateValues" dxfId="626" priority="617"/>
-    <cfRule type="duplicateValues" dxfId="625" priority="616"/>
-    <cfRule type="duplicateValues" dxfId="624" priority="615"/>
-    <cfRule type="duplicateValues" dxfId="623" priority="614"/>
+    <cfRule type="duplicateValues" dxfId="628" priority="621"/>
+    <cfRule type="duplicateValues" dxfId="627" priority="622"/>
+    <cfRule type="duplicateValues" dxfId="626" priority="623"/>
+    <cfRule type="duplicateValues" dxfId="625" priority="624"/>
+    <cfRule type="duplicateValues" dxfId="624" priority="625"/>
+    <cfRule type="duplicateValues" dxfId="623" priority="626"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2352">
+  <conditionalFormatting sqref="A2352">
     <cfRule type="duplicateValues" dxfId="622" priority="601"/>
     <cfRule type="duplicateValues" dxfId="621" priority="602"/>
-    <cfRule type="duplicateValues" dxfId="620" priority="613"/>
-    <cfRule type="duplicateValues" dxfId="619" priority="612"/>
-    <cfRule type="duplicateValues" dxfId="618" priority="611"/>
-    <cfRule type="duplicateValues" dxfId="617" priority="610"/>
-    <cfRule type="duplicateValues" dxfId="616" priority="609"/>
+    <cfRule type="duplicateValues" dxfId="620" priority="603"/>
+    <cfRule type="duplicateValues" dxfId="619" priority="604"/>
+    <cfRule type="duplicateValues" dxfId="618" priority="605"/>
+    <cfRule type="duplicateValues" dxfId="617" priority="606"/>
+    <cfRule type="duplicateValues" dxfId="616" priority="607"/>
     <cfRule type="duplicateValues" dxfId="615" priority="608"/>
-    <cfRule type="duplicateValues" dxfId="614" priority="607"/>
-    <cfRule type="duplicateValues" dxfId="613" priority="606"/>
-    <cfRule type="duplicateValues" dxfId="612" priority="605"/>
-    <cfRule type="duplicateValues" dxfId="611" priority="604"/>
-    <cfRule type="duplicateValues" dxfId="610" priority="603"/>
+    <cfRule type="duplicateValues" dxfId="614" priority="609"/>
+    <cfRule type="duplicateValues" dxfId="613" priority="610"/>
+    <cfRule type="duplicateValues" dxfId="612" priority="611"/>
+    <cfRule type="duplicateValues" dxfId="611" priority="612"/>
+    <cfRule type="duplicateValues" dxfId="610" priority="613"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2354">
-    <cfRule type="duplicateValues" dxfId="609" priority="599"/>
-    <cfRule type="duplicateValues" dxfId="608" priority="600"/>
-    <cfRule type="duplicateValues" dxfId="607" priority="588"/>
-    <cfRule type="duplicateValues" dxfId="606" priority="589"/>
-    <cfRule type="duplicateValues" dxfId="605" priority="590"/>
-    <cfRule type="duplicateValues" dxfId="604" priority="591"/>
-    <cfRule type="duplicateValues" dxfId="603" priority="592"/>
-    <cfRule type="duplicateValues" dxfId="602" priority="593"/>
-    <cfRule type="duplicateValues" dxfId="601" priority="594"/>
-    <cfRule type="duplicateValues" dxfId="600" priority="595"/>
-    <cfRule type="duplicateValues" dxfId="599" priority="596"/>
-    <cfRule type="duplicateValues" dxfId="598" priority="597"/>
-    <cfRule type="duplicateValues" dxfId="597" priority="598"/>
+  <conditionalFormatting sqref="A2354">
+    <cfRule type="duplicateValues" dxfId="609" priority="588"/>
+    <cfRule type="duplicateValues" dxfId="608" priority="589"/>
+    <cfRule type="duplicateValues" dxfId="607" priority="590"/>
+    <cfRule type="duplicateValues" dxfId="606" priority="591"/>
+    <cfRule type="duplicateValues" dxfId="605" priority="592"/>
+    <cfRule type="duplicateValues" dxfId="604" priority="593"/>
+    <cfRule type="duplicateValues" dxfId="603" priority="594"/>
+    <cfRule type="duplicateValues" dxfId="602" priority="595"/>
+    <cfRule type="duplicateValues" dxfId="601" priority="596"/>
+    <cfRule type="duplicateValues" dxfId="600" priority="597"/>
+    <cfRule type="duplicateValues" dxfId="599" priority="598"/>
+    <cfRule type="duplicateValues" dxfId="598" priority="599"/>
+    <cfRule type="duplicateValues" dxfId="597" priority="600"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2355">
-    <cfRule type="duplicateValues" dxfId="596" priority="583"/>
+  <conditionalFormatting sqref="A2355">
+    <cfRule type="duplicateValues" dxfId="596" priority="575"/>
     <cfRule type="duplicateValues" dxfId="595" priority="576"/>
-    <cfRule type="duplicateValues" dxfId="594" priority="587"/>
-    <cfRule type="duplicateValues" dxfId="593" priority="586"/>
-    <cfRule type="duplicateValues" dxfId="592" priority="585"/>
-    <cfRule type="duplicateValues" dxfId="591" priority="584"/>
-    <cfRule type="duplicateValues" dxfId="590" priority="577"/>
+    <cfRule type="duplicateValues" dxfId="594" priority="577"/>
+    <cfRule type="duplicateValues" dxfId="593" priority="578"/>
+    <cfRule type="duplicateValues" dxfId="592" priority="579"/>
+    <cfRule type="duplicateValues" dxfId="591" priority="580"/>
+    <cfRule type="duplicateValues" dxfId="590" priority="581"/>
     <cfRule type="duplicateValues" dxfId="589" priority="582"/>
-    <cfRule type="duplicateValues" dxfId="588" priority="581"/>
-    <cfRule type="duplicateValues" dxfId="587" priority="580"/>
-    <cfRule type="duplicateValues" dxfId="586" priority="579"/>
-    <cfRule type="duplicateValues" dxfId="585" priority="578"/>
-    <cfRule type="duplicateValues" dxfId="584" priority="575"/>
+    <cfRule type="duplicateValues" dxfId="588" priority="583"/>
+    <cfRule type="duplicateValues" dxfId="587" priority="584"/>
+    <cfRule type="duplicateValues" dxfId="586" priority="585"/>
+    <cfRule type="duplicateValues" dxfId="585" priority="586"/>
+    <cfRule type="duplicateValues" dxfId="584" priority="587"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2356">
-    <cfRule type="duplicateValues" dxfId="583" priority="563"/>
-    <cfRule type="duplicateValues" dxfId="582" priority="573"/>
-    <cfRule type="duplicateValues" dxfId="581" priority="574"/>
-    <cfRule type="duplicateValues" dxfId="580" priority="562"/>
-    <cfRule type="duplicateValues" dxfId="579" priority="572"/>
-    <cfRule type="duplicateValues" dxfId="578" priority="571"/>
-    <cfRule type="duplicateValues" dxfId="577" priority="570"/>
+  <conditionalFormatting sqref="A2356">
+    <cfRule type="duplicateValues" dxfId="583" priority="562"/>
+    <cfRule type="duplicateValues" dxfId="582" priority="563"/>
+    <cfRule type="duplicateValues" dxfId="581" priority="564"/>
+    <cfRule type="duplicateValues" dxfId="580" priority="565"/>
+    <cfRule type="duplicateValues" dxfId="579" priority="566"/>
+    <cfRule type="duplicateValues" dxfId="578" priority="567"/>
+    <cfRule type="duplicateValues" dxfId="577" priority="568"/>
     <cfRule type="duplicateValues" dxfId="576" priority="569"/>
-    <cfRule type="duplicateValues" dxfId="575" priority="568"/>
-    <cfRule type="duplicateValues" dxfId="574" priority="567"/>
-    <cfRule type="duplicateValues" dxfId="573" priority="566"/>
-    <cfRule type="duplicateValues" dxfId="572" priority="565"/>
-    <cfRule type="duplicateValues" dxfId="571" priority="564"/>
+    <cfRule type="duplicateValues" dxfId="575" priority="570"/>
+    <cfRule type="duplicateValues" dxfId="574" priority="571"/>
+    <cfRule type="duplicateValues" dxfId="573" priority="572"/>
+    <cfRule type="duplicateValues" dxfId="572" priority="573"/>
+    <cfRule type="duplicateValues" dxfId="571" priority="574"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2357">
-    <cfRule type="duplicateValues" dxfId="570" priority="552"/>
-    <cfRule type="duplicateValues" dxfId="569" priority="561"/>
-    <cfRule type="duplicateValues" dxfId="568" priority="560"/>
-    <cfRule type="duplicateValues" dxfId="567" priority="559"/>
-    <cfRule type="duplicateValues" dxfId="566" priority="558"/>
-    <cfRule type="duplicateValues" dxfId="565" priority="557"/>
-    <cfRule type="duplicateValues" dxfId="564" priority="556"/>
-    <cfRule type="duplicateValues" dxfId="563" priority="555"/>
-    <cfRule type="duplicateValues" dxfId="562" priority="554"/>
-    <cfRule type="duplicateValues" dxfId="561" priority="553"/>
-    <cfRule type="duplicateValues" dxfId="560" priority="551"/>
-    <cfRule type="duplicateValues" dxfId="559" priority="550"/>
-    <cfRule type="duplicateValues" dxfId="558" priority="549"/>
+  <conditionalFormatting sqref="A2357">
+    <cfRule type="duplicateValues" dxfId="570" priority="549"/>
+    <cfRule type="duplicateValues" dxfId="569" priority="550"/>
+    <cfRule type="duplicateValues" dxfId="568" priority="551"/>
+    <cfRule type="duplicateValues" dxfId="567" priority="552"/>
+    <cfRule type="duplicateValues" dxfId="566" priority="553"/>
+    <cfRule type="duplicateValues" dxfId="565" priority="554"/>
+    <cfRule type="duplicateValues" dxfId="564" priority="555"/>
+    <cfRule type="duplicateValues" dxfId="563" priority="556"/>
+    <cfRule type="duplicateValues" dxfId="562" priority="557"/>
+    <cfRule type="duplicateValues" dxfId="561" priority="558"/>
+    <cfRule type="duplicateValues" dxfId="560" priority="559"/>
+    <cfRule type="duplicateValues" dxfId="559" priority="560"/>
+    <cfRule type="duplicateValues" dxfId="558" priority="561"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2364">
-    <cfRule type="duplicateValues" dxfId="557" priority="536"/>
+  <conditionalFormatting sqref="A2364">
+    <cfRule type="duplicateValues" dxfId="557" priority="534"/>
     <cfRule type="duplicateValues" dxfId="556" priority="535"/>
-    <cfRule type="duplicateValues" dxfId="555" priority="534"/>
-    <cfRule type="duplicateValues" dxfId="554" priority="547"/>
-    <cfRule type="duplicateValues" dxfId="553" priority="546"/>
-    <cfRule type="duplicateValues" dxfId="552" priority="545"/>
-    <cfRule type="duplicateValues" dxfId="551" priority="544"/>
-    <cfRule type="duplicateValues" dxfId="550" priority="543"/>
+    <cfRule type="duplicateValues" dxfId="555" priority="536"/>
+    <cfRule type="duplicateValues" dxfId="554" priority="537"/>
+    <cfRule type="duplicateValues" dxfId="553" priority="538"/>
+    <cfRule type="duplicateValues" dxfId="552" priority="539"/>
+    <cfRule type="duplicateValues" dxfId="551" priority="540"/>
+    <cfRule type="duplicateValues" dxfId="550" priority="541"/>
     <cfRule type="duplicateValues" dxfId="549" priority="542"/>
-    <cfRule type="duplicateValues" dxfId="548" priority="541"/>
-    <cfRule type="duplicateValues" dxfId="547" priority="540"/>
-    <cfRule type="duplicateValues" dxfId="546" priority="539"/>
-    <cfRule type="duplicateValues" dxfId="545" priority="538"/>
-    <cfRule type="duplicateValues" dxfId="544" priority="537"/>
+    <cfRule type="duplicateValues" dxfId="548" priority="543"/>
+    <cfRule type="duplicateValues" dxfId="547" priority="544"/>
+    <cfRule type="duplicateValues" dxfId="546" priority="545"/>
+    <cfRule type="duplicateValues" dxfId="545" priority="546"/>
+    <cfRule type="duplicateValues" dxfId="544" priority="547"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2372">
-    <cfRule type="duplicateValues" dxfId="543" priority="521"/>
-    <cfRule type="duplicateValues" dxfId="542" priority="520"/>
-    <cfRule type="duplicateValues" dxfId="541" priority="519"/>
-    <cfRule type="duplicateValues" dxfId="540" priority="518"/>
-    <cfRule type="duplicateValues" dxfId="539" priority="532"/>
-    <cfRule type="duplicateValues" dxfId="538" priority="531"/>
-    <cfRule type="duplicateValues" dxfId="537" priority="530"/>
-    <cfRule type="duplicateValues" dxfId="536" priority="529"/>
-    <cfRule type="duplicateValues" dxfId="535" priority="528"/>
+  <conditionalFormatting sqref="A2372">
+    <cfRule type="duplicateValues" dxfId="543" priority="518"/>
+    <cfRule type="duplicateValues" dxfId="542" priority="519"/>
+    <cfRule type="duplicateValues" dxfId="541" priority="520"/>
+    <cfRule type="duplicateValues" dxfId="540" priority="521"/>
+    <cfRule type="duplicateValues" dxfId="539" priority="522"/>
+    <cfRule type="duplicateValues" dxfId="538" priority="523"/>
+    <cfRule type="duplicateValues" dxfId="537" priority="524"/>
+    <cfRule type="duplicateValues" dxfId="536" priority="525"/>
+    <cfRule type="duplicateValues" dxfId="535" priority="526"/>
     <cfRule type="duplicateValues" dxfId="534" priority="527"/>
-    <cfRule type="duplicateValues" dxfId="533" priority="526"/>
-    <cfRule type="duplicateValues" dxfId="532" priority="525"/>
-    <cfRule type="duplicateValues" dxfId="531" priority="524"/>
-    <cfRule type="duplicateValues" dxfId="530" priority="523"/>
-    <cfRule type="duplicateValues" dxfId="529" priority="522"/>
+    <cfRule type="duplicateValues" dxfId="533" priority="528"/>
+    <cfRule type="duplicateValues" dxfId="532" priority="529"/>
+    <cfRule type="duplicateValues" dxfId="531" priority="530"/>
+    <cfRule type="duplicateValues" dxfId="530" priority="531"/>
+    <cfRule type="duplicateValues" dxfId="529" priority="532"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2373">
-    <cfRule type="duplicateValues" dxfId="528" priority="514"/>
-    <cfRule type="duplicateValues" dxfId="527" priority="515"/>
-    <cfRule type="duplicateValues" dxfId="526" priority="506"/>
-    <cfRule type="duplicateValues" dxfId="525" priority="505"/>
-    <cfRule type="duplicateValues" dxfId="524" priority="517"/>
-    <cfRule type="duplicateValues" dxfId="523" priority="516"/>
-    <cfRule type="duplicateValues" dxfId="522" priority="504"/>
-    <cfRule type="duplicateValues" dxfId="521" priority="507"/>
-    <cfRule type="duplicateValues" dxfId="520" priority="513"/>
+  <conditionalFormatting sqref="A2373">
+    <cfRule type="duplicateValues" dxfId="528" priority="503"/>
+    <cfRule type="duplicateValues" dxfId="527" priority="504"/>
+    <cfRule type="duplicateValues" dxfId="526" priority="505"/>
+    <cfRule type="duplicateValues" dxfId="525" priority="506"/>
+    <cfRule type="duplicateValues" dxfId="524" priority="507"/>
+    <cfRule type="duplicateValues" dxfId="523" priority="508"/>
+    <cfRule type="duplicateValues" dxfId="522" priority="509"/>
+    <cfRule type="duplicateValues" dxfId="521" priority="510"/>
+    <cfRule type="duplicateValues" dxfId="520" priority="511"/>
     <cfRule type="duplicateValues" dxfId="519" priority="512"/>
-    <cfRule type="duplicateValues" dxfId="518" priority="511"/>
-    <cfRule type="duplicateValues" dxfId="517" priority="510"/>
-    <cfRule type="duplicateValues" dxfId="516" priority="509"/>
-    <cfRule type="duplicateValues" dxfId="515" priority="508"/>
-    <cfRule type="duplicateValues" dxfId="514" priority="503"/>
+    <cfRule type="duplicateValues" dxfId="518" priority="513"/>
+    <cfRule type="duplicateValues" dxfId="517" priority="514"/>
+    <cfRule type="duplicateValues" dxfId="516" priority="515"/>
+    <cfRule type="duplicateValues" dxfId="515" priority="516"/>
+    <cfRule type="duplicateValues" dxfId="514" priority="517"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2389:D2390">
-    <cfRule type="duplicateValues" dxfId="513" priority="490"/>
-    <cfRule type="duplicateValues" dxfId="512" priority="489"/>
+  <conditionalFormatting sqref="A2389:A2390">
+    <cfRule type="duplicateValues" dxfId="513" priority="486"/>
+    <cfRule type="duplicateValues" dxfId="512" priority="487"/>
     <cfRule type="duplicateValues" dxfId="511" priority="488"/>
-    <cfRule type="duplicateValues" dxfId="510" priority="487"/>
-    <cfRule type="duplicateValues" dxfId="509" priority="486"/>
-    <cfRule type="duplicateValues" dxfId="508" priority="501"/>
-    <cfRule type="duplicateValues" dxfId="507" priority="500"/>
-    <cfRule type="duplicateValues" dxfId="506" priority="499"/>
-    <cfRule type="duplicateValues" dxfId="505" priority="498"/>
-    <cfRule type="duplicateValues" dxfId="504" priority="497"/>
+    <cfRule type="duplicateValues" dxfId="510" priority="489"/>
+    <cfRule type="duplicateValues" dxfId="509" priority="490"/>
+    <cfRule type="duplicateValues" dxfId="508" priority="491"/>
+    <cfRule type="duplicateValues" dxfId="507" priority="492"/>
+    <cfRule type="duplicateValues" dxfId="506" priority="493"/>
+    <cfRule type="duplicateValues" dxfId="505" priority="494"/>
+    <cfRule type="duplicateValues" dxfId="504" priority="495"/>
     <cfRule type="duplicateValues" dxfId="503" priority="496"/>
-    <cfRule type="duplicateValues" dxfId="502" priority="495"/>
-    <cfRule type="duplicateValues" dxfId="501" priority="494"/>
-    <cfRule type="duplicateValues" dxfId="500" priority="493"/>
-    <cfRule type="duplicateValues" dxfId="499" priority="492"/>
-    <cfRule type="duplicateValues" dxfId="498" priority="491"/>
+    <cfRule type="duplicateValues" dxfId="502" priority="497"/>
+    <cfRule type="duplicateValues" dxfId="501" priority="498"/>
+    <cfRule type="duplicateValues" dxfId="500" priority="499"/>
+    <cfRule type="duplicateValues" dxfId="499" priority="500"/>
+    <cfRule type="duplicateValues" dxfId="498" priority="501"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2391">
-    <cfRule type="duplicateValues" dxfId="497" priority="485"/>
-    <cfRule type="duplicateValues" dxfId="496" priority="484"/>
-    <cfRule type="duplicateValues" dxfId="495" priority="483"/>
-    <cfRule type="duplicateValues" dxfId="494" priority="482"/>
-    <cfRule type="duplicateValues" dxfId="493" priority="481"/>
-    <cfRule type="duplicateValues" dxfId="492" priority="480"/>
-    <cfRule type="duplicateValues" dxfId="491" priority="479"/>
-    <cfRule type="duplicateValues" dxfId="490" priority="478"/>
-    <cfRule type="duplicateValues" dxfId="489" priority="477"/>
-    <cfRule type="duplicateValues" dxfId="488" priority="476"/>
-    <cfRule type="duplicateValues" dxfId="487" priority="475"/>
-    <cfRule type="duplicateValues" dxfId="486" priority="474"/>
-    <cfRule type="duplicateValues" dxfId="485" priority="473"/>
-    <cfRule type="duplicateValues" dxfId="484" priority="472"/>
-    <cfRule type="duplicateValues" dxfId="483" priority="471"/>
-    <cfRule type="duplicateValues" dxfId="482" priority="470"/>
+  <conditionalFormatting sqref="A2391">
+    <cfRule type="duplicateValues" dxfId="497" priority="470"/>
+    <cfRule type="duplicateValues" dxfId="496" priority="471"/>
+    <cfRule type="duplicateValues" dxfId="495" priority="472"/>
+    <cfRule type="duplicateValues" dxfId="494" priority="473"/>
+    <cfRule type="duplicateValues" dxfId="493" priority="474"/>
+    <cfRule type="duplicateValues" dxfId="492" priority="475"/>
+    <cfRule type="duplicateValues" dxfId="491" priority="476"/>
+    <cfRule type="duplicateValues" dxfId="490" priority="477"/>
+    <cfRule type="duplicateValues" dxfId="489" priority="478"/>
+    <cfRule type="duplicateValues" dxfId="488" priority="479"/>
+    <cfRule type="duplicateValues" dxfId="487" priority="480"/>
+    <cfRule type="duplicateValues" dxfId="486" priority="481"/>
+    <cfRule type="duplicateValues" dxfId="485" priority="482"/>
+    <cfRule type="duplicateValues" dxfId="484" priority="483"/>
+    <cfRule type="duplicateValues" dxfId="483" priority="484"/>
+    <cfRule type="duplicateValues" dxfId="482" priority="485"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2392">
-    <cfRule type="duplicateValues" dxfId="481" priority="457"/>
-    <cfRule type="duplicateValues" dxfId="480" priority="456"/>
-    <cfRule type="duplicateValues" dxfId="479" priority="455"/>
-    <cfRule type="duplicateValues" dxfId="478" priority="458"/>
-    <cfRule type="duplicateValues" dxfId="477" priority="454"/>
-    <cfRule type="duplicateValues" dxfId="476" priority="469"/>
-    <cfRule type="duplicateValues" dxfId="475" priority="468"/>
-    <cfRule type="duplicateValues" dxfId="474" priority="467"/>
-    <cfRule type="duplicateValues" dxfId="473" priority="466"/>
-    <cfRule type="duplicateValues" dxfId="472" priority="465"/>
+  <conditionalFormatting sqref="A2392">
+    <cfRule type="duplicateValues" dxfId="481" priority="454"/>
+    <cfRule type="duplicateValues" dxfId="480" priority="455"/>
+    <cfRule type="duplicateValues" dxfId="479" priority="456"/>
+    <cfRule type="duplicateValues" dxfId="478" priority="457"/>
+    <cfRule type="duplicateValues" dxfId="477" priority="458"/>
+    <cfRule type="duplicateValues" dxfId="476" priority="459"/>
+    <cfRule type="duplicateValues" dxfId="475" priority="460"/>
+    <cfRule type="duplicateValues" dxfId="474" priority="461"/>
+    <cfRule type="duplicateValues" dxfId="473" priority="462"/>
+    <cfRule type="duplicateValues" dxfId="472" priority="463"/>
     <cfRule type="duplicateValues" dxfId="471" priority="464"/>
-    <cfRule type="duplicateValues" dxfId="470" priority="463"/>
-    <cfRule type="duplicateValues" dxfId="469" priority="462"/>
-    <cfRule type="duplicateValues" dxfId="468" priority="461"/>
-    <cfRule type="duplicateValues" dxfId="467" priority="460"/>
-    <cfRule type="duplicateValues" dxfId="466" priority="459"/>
+    <cfRule type="duplicateValues" dxfId="470" priority="465"/>
+    <cfRule type="duplicateValues" dxfId="469" priority="466"/>
+    <cfRule type="duplicateValues" dxfId="468" priority="467"/>
+    <cfRule type="duplicateValues" dxfId="467" priority="468"/>
+    <cfRule type="duplicateValues" dxfId="466" priority="469"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2429">
-    <cfRule type="duplicateValues" dxfId="465" priority="441"/>
-    <cfRule type="duplicateValues" dxfId="464" priority="438"/>
+  <conditionalFormatting sqref="A2429">
+    <cfRule type="duplicateValues" dxfId="465" priority="438"/>
+    <cfRule type="duplicateValues" dxfId="464" priority="439"/>
     <cfRule type="duplicateValues" dxfId="463" priority="440"/>
-    <cfRule type="duplicateValues" dxfId="462" priority="449"/>
-    <cfRule type="duplicateValues" dxfId="461" priority="439"/>
-    <cfRule type="duplicateValues" dxfId="460" priority="453"/>
-    <cfRule type="duplicateValues" dxfId="459" priority="452"/>
-    <cfRule type="duplicateValues" dxfId="458" priority="451"/>
-    <cfRule type="duplicateValues" dxfId="457" priority="450"/>
-    <cfRule type="duplicateValues" dxfId="456" priority="448"/>
-    <cfRule type="duplicateValues" dxfId="455" priority="447"/>
-    <cfRule type="duplicateValues" dxfId="454" priority="446"/>
-    <cfRule type="duplicateValues" dxfId="453" priority="445"/>
-    <cfRule type="duplicateValues" dxfId="452" priority="444"/>
-    <cfRule type="duplicateValues" dxfId="451" priority="443"/>
-    <cfRule type="duplicateValues" dxfId="450" priority="442"/>
+    <cfRule type="duplicateValues" dxfId="462" priority="441"/>
+    <cfRule type="duplicateValues" dxfId="461" priority="442"/>
+    <cfRule type="duplicateValues" dxfId="460" priority="443"/>
+    <cfRule type="duplicateValues" dxfId="459" priority="444"/>
+    <cfRule type="duplicateValues" dxfId="458" priority="445"/>
+    <cfRule type="duplicateValues" dxfId="457" priority="446"/>
+    <cfRule type="duplicateValues" dxfId="456" priority="447"/>
+    <cfRule type="duplicateValues" dxfId="455" priority="448"/>
+    <cfRule type="duplicateValues" dxfId="454" priority="449"/>
+    <cfRule type="duplicateValues" dxfId="453" priority="450"/>
+    <cfRule type="duplicateValues" dxfId="452" priority="451"/>
+    <cfRule type="duplicateValues" dxfId="451" priority="452"/>
+    <cfRule type="duplicateValues" dxfId="450" priority="453"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2430">
-    <cfRule type="duplicateValues" dxfId="449" priority="423"/>
-    <cfRule type="duplicateValues" dxfId="448" priority="426"/>
-    <cfRule type="duplicateValues" dxfId="447" priority="425"/>
-    <cfRule type="duplicateValues" dxfId="446" priority="424"/>
-    <cfRule type="duplicateValues" dxfId="445" priority="422"/>
-    <cfRule type="duplicateValues" dxfId="444" priority="437"/>
-    <cfRule type="duplicateValues" dxfId="443" priority="436"/>
-    <cfRule type="duplicateValues" dxfId="442" priority="435"/>
-    <cfRule type="duplicateValues" dxfId="441" priority="434"/>
-    <cfRule type="duplicateValues" dxfId="440" priority="433"/>
+  <conditionalFormatting sqref="A2430">
+    <cfRule type="duplicateValues" dxfId="449" priority="422"/>
+    <cfRule type="duplicateValues" dxfId="448" priority="423"/>
+    <cfRule type="duplicateValues" dxfId="447" priority="424"/>
+    <cfRule type="duplicateValues" dxfId="446" priority="425"/>
+    <cfRule type="duplicateValues" dxfId="445" priority="426"/>
+    <cfRule type="duplicateValues" dxfId="444" priority="427"/>
+    <cfRule type="duplicateValues" dxfId="443" priority="428"/>
+    <cfRule type="duplicateValues" dxfId="442" priority="429"/>
+    <cfRule type="duplicateValues" dxfId="441" priority="430"/>
+    <cfRule type="duplicateValues" dxfId="440" priority="431"/>
     <cfRule type="duplicateValues" dxfId="439" priority="432"/>
-    <cfRule type="duplicateValues" dxfId="438" priority="431"/>
-    <cfRule type="duplicateValues" dxfId="437" priority="430"/>
-    <cfRule type="duplicateValues" dxfId="436" priority="429"/>
-    <cfRule type="duplicateValues" dxfId="435" priority="428"/>
-    <cfRule type="duplicateValues" dxfId="434" priority="427"/>
+    <cfRule type="duplicateValues" dxfId="438" priority="433"/>
+    <cfRule type="duplicateValues" dxfId="437" priority="434"/>
+    <cfRule type="duplicateValues" dxfId="436" priority="435"/>
+    <cfRule type="duplicateValues" dxfId="435" priority="436"/>
+    <cfRule type="duplicateValues" dxfId="434" priority="437"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2431">
-    <cfRule type="duplicateValues" dxfId="433" priority="410"/>
-    <cfRule type="duplicateValues" dxfId="432" priority="409"/>
+  <conditionalFormatting sqref="A2431">
+    <cfRule type="duplicateValues" dxfId="433" priority="406"/>
+    <cfRule type="duplicateValues" dxfId="432" priority="407"/>
     <cfRule type="duplicateValues" dxfId="431" priority="408"/>
-    <cfRule type="duplicateValues" dxfId="430" priority="407"/>
-    <cfRule type="duplicateValues" dxfId="429" priority="406"/>
-    <cfRule type="duplicateValues" dxfId="428" priority="421"/>
-    <cfRule type="duplicateValues" dxfId="427" priority="420"/>
-    <cfRule type="duplicateValues" dxfId="426" priority="419"/>
-    <cfRule type="duplicateValues" dxfId="425" priority="418"/>
-    <cfRule type="duplicateValues" dxfId="424" priority="417"/>
+    <cfRule type="duplicateValues" dxfId="430" priority="409"/>
+    <cfRule type="duplicateValues" dxfId="429" priority="410"/>
+    <cfRule type="duplicateValues" dxfId="428" priority="411"/>
+    <cfRule type="duplicateValues" dxfId="427" priority="412"/>
+    <cfRule type="duplicateValues" dxfId="426" priority="413"/>
+    <cfRule type="duplicateValues" dxfId="425" priority="414"/>
+    <cfRule type="duplicateValues" dxfId="424" priority="415"/>
     <cfRule type="duplicateValues" dxfId="423" priority="416"/>
-    <cfRule type="duplicateValues" dxfId="422" priority="415"/>
-    <cfRule type="duplicateValues" dxfId="421" priority="414"/>
-    <cfRule type="duplicateValues" dxfId="420" priority="413"/>
-    <cfRule type="duplicateValues" dxfId="419" priority="412"/>
-    <cfRule type="duplicateValues" dxfId="418" priority="411"/>
+    <cfRule type="duplicateValues" dxfId="422" priority="417"/>
+    <cfRule type="duplicateValues" dxfId="421" priority="418"/>
+    <cfRule type="duplicateValues" dxfId="420" priority="419"/>
+    <cfRule type="duplicateValues" dxfId="419" priority="420"/>
+    <cfRule type="duplicateValues" dxfId="418" priority="421"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2432">
-    <cfRule type="duplicateValues" dxfId="417" priority="404"/>
-    <cfRule type="duplicateValues" dxfId="416" priority="405"/>
-    <cfRule type="duplicateValues" dxfId="415" priority="403"/>
-    <cfRule type="duplicateValues" dxfId="414" priority="402"/>
-    <cfRule type="duplicateValues" dxfId="413" priority="401"/>
-    <cfRule type="duplicateValues" dxfId="412" priority="400"/>
-    <cfRule type="duplicateValues" dxfId="411" priority="399"/>
-    <cfRule type="duplicateValues" dxfId="410" priority="398"/>
-    <cfRule type="duplicateValues" dxfId="409" priority="397"/>
-    <cfRule type="duplicateValues" dxfId="408" priority="396"/>
-    <cfRule type="duplicateValues" dxfId="407" priority="395"/>
-    <cfRule type="duplicateValues" dxfId="406" priority="394"/>
-    <cfRule type="duplicateValues" dxfId="405" priority="393"/>
-    <cfRule type="duplicateValues" dxfId="404" priority="392"/>
-    <cfRule type="duplicateValues" dxfId="403" priority="391"/>
-    <cfRule type="duplicateValues" dxfId="402" priority="390"/>
+  <conditionalFormatting sqref="A2432">
+    <cfRule type="duplicateValues" dxfId="417" priority="390"/>
+    <cfRule type="duplicateValues" dxfId="416" priority="391"/>
+    <cfRule type="duplicateValues" dxfId="415" priority="392"/>
+    <cfRule type="duplicateValues" dxfId="414" priority="393"/>
+    <cfRule type="duplicateValues" dxfId="413" priority="394"/>
+    <cfRule type="duplicateValues" dxfId="412" priority="395"/>
+    <cfRule type="duplicateValues" dxfId="411" priority="396"/>
+    <cfRule type="duplicateValues" dxfId="410" priority="397"/>
+    <cfRule type="duplicateValues" dxfId="409" priority="398"/>
+    <cfRule type="duplicateValues" dxfId="408" priority="399"/>
+    <cfRule type="duplicateValues" dxfId="407" priority="400"/>
+    <cfRule type="duplicateValues" dxfId="406" priority="401"/>
+    <cfRule type="duplicateValues" dxfId="405" priority="402"/>
+    <cfRule type="duplicateValues" dxfId="404" priority="403"/>
+    <cfRule type="duplicateValues" dxfId="403" priority="404"/>
+    <cfRule type="duplicateValues" dxfId="402" priority="405"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2434">
-    <cfRule type="duplicateValues" dxfId="401" priority="378"/>
-    <cfRule type="duplicateValues" dxfId="400" priority="377"/>
+  <conditionalFormatting sqref="A2434">
+    <cfRule type="duplicateValues" dxfId="401" priority="374"/>
+    <cfRule type="duplicateValues" dxfId="400" priority="375"/>
     <cfRule type="duplicateValues" dxfId="399" priority="376"/>
-    <cfRule type="duplicateValues" dxfId="398" priority="375"/>
-    <cfRule type="duplicateValues" dxfId="397" priority="374"/>
-    <cfRule type="duplicateValues" dxfId="396" priority="389"/>
-    <cfRule type="duplicateValues" dxfId="395" priority="388"/>
-    <cfRule type="duplicateValues" dxfId="394" priority="387"/>
-    <cfRule type="duplicateValues" dxfId="393" priority="386"/>
-    <cfRule type="duplicateValues" dxfId="392" priority="385"/>
+    <cfRule type="duplicateValues" dxfId="398" priority="377"/>
+    <cfRule type="duplicateValues" dxfId="397" priority="378"/>
+    <cfRule type="duplicateValues" dxfId="396" priority="379"/>
+    <cfRule type="duplicateValues" dxfId="395" priority="380"/>
+    <cfRule type="duplicateValues" dxfId="394" priority="381"/>
+    <cfRule type="duplicateValues" dxfId="393" priority="382"/>
+    <cfRule type="duplicateValues" dxfId="392" priority="383"/>
     <cfRule type="duplicateValues" dxfId="391" priority="384"/>
-    <cfRule type="duplicateValues" dxfId="390" priority="383"/>
-    <cfRule type="duplicateValues" dxfId="389" priority="382"/>
-    <cfRule type="duplicateValues" dxfId="388" priority="381"/>
-    <cfRule type="duplicateValues" dxfId="387" priority="380"/>
-    <cfRule type="duplicateValues" dxfId="386" priority="379"/>
+    <cfRule type="duplicateValues" dxfId="390" priority="385"/>
+    <cfRule type="duplicateValues" dxfId="389" priority="386"/>
+    <cfRule type="duplicateValues" dxfId="388" priority="387"/>
+    <cfRule type="duplicateValues" dxfId="387" priority="388"/>
+    <cfRule type="duplicateValues" dxfId="386" priority="389"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2435">
-    <cfRule type="duplicateValues" dxfId="385" priority="361"/>
-    <cfRule type="duplicateValues" dxfId="384" priority="360"/>
-    <cfRule type="duplicateValues" dxfId="383" priority="359"/>
-    <cfRule type="duplicateValues" dxfId="382" priority="358"/>
-    <cfRule type="duplicateValues" dxfId="381" priority="357"/>
-    <cfRule type="duplicateValues" dxfId="380" priority="356"/>
-    <cfRule type="duplicateValues" dxfId="379" priority="372"/>
-    <cfRule type="duplicateValues" dxfId="378" priority="371"/>
-    <cfRule type="duplicateValues" dxfId="377" priority="370"/>
-    <cfRule type="duplicateValues" dxfId="376" priority="369"/>
-    <cfRule type="duplicateValues" dxfId="375" priority="368"/>
+  <conditionalFormatting sqref="A2435">
+    <cfRule type="duplicateValues" dxfId="385" priority="356"/>
+    <cfRule type="duplicateValues" dxfId="384" priority="357"/>
+    <cfRule type="duplicateValues" dxfId="383" priority="358"/>
+    <cfRule type="duplicateValues" dxfId="382" priority="359"/>
+    <cfRule type="duplicateValues" dxfId="381" priority="360"/>
+    <cfRule type="duplicateValues" dxfId="380" priority="361"/>
+    <cfRule type="duplicateValues" dxfId="379" priority="362"/>
+    <cfRule type="duplicateValues" dxfId="378" priority="363"/>
+    <cfRule type="duplicateValues" dxfId="377" priority="364"/>
+    <cfRule type="duplicateValues" dxfId="376" priority="365"/>
+    <cfRule type="duplicateValues" dxfId="375" priority="366"/>
     <cfRule type="duplicateValues" dxfId="374" priority="367"/>
-    <cfRule type="duplicateValues" dxfId="373" priority="366"/>
-    <cfRule type="duplicateValues" dxfId="372" priority="365"/>
-    <cfRule type="duplicateValues" dxfId="371" priority="364"/>
-    <cfRule type="duplicateValues" dxfId="370" priority="363"/>
-    <cfRule type="duplicateValues" dxfId="369" priority="362"/>
+    <cfRule type="duplicateValues" dxfId="373" priority="368"/>
+    <cfRule type="duplicateValues" dxfId="372" priority="369"/>
+    <cfRule type="duplicateValues" dxfId="371" priority="370"/>
+    <cfRule type="duplicateValues" dxfId="370" priority="371"/>
+    <cfRule type="duplicateValues" dxfId="369" priority="372"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2441">
-    <cfRule type="duplicateValues" dxfId="368" priority="352"/>
-    <cfRule type="duplicateValues" dxfId="367" priority="340"/>
-    <cfRule type="duplicateValues" dxfId="366" priority="341"/>
-    <cfRule type="duplicateValues" dxfId="365" priority="342"/>
-    <cfRule type="duplicateValues" dxfId="364" priority="354"/>
-    <cfRule type="duplicateValues" dxfId="363" priority="353"/>
+  <conditionalFormatting sqref="A2441">
+    <cfRule type="duplicateValues" dxfId="368" priority="337"/>
+    <cfRule type="duplicateValues" dxfId="367" priority="338"/>
+    <cfRule type="duplicateValues" dxfId="366" priority="339"/>
+    <cfRule type="duplicateValues" dxfId="365" priority="340"/>
+    <cfRule type="duplicateValues" dxfId="364" priority="341"/>
+    <cfRule type="duplicateValues" dxfId="363" priority="342"/>
     <cfRule type="duplicateValues" dxfId="362" priority="343"/>
-    <cfRule type="duplicateValues" dxfId="361" priority="351"/>
-    <cfRule type="duplicateValues" dxfId="360" priority="350"/>
-    <cfRule type="duplicateValues" dxfId="359" priority="349"/>
-    <cfRule type="duplicateValues" dxfId="358" priority="348"/>
-    <cfRule type="duplicateValues" dxfId="357" priority="347"/>
-    <cfRule type="duplicateValues" dxfId="356" priority="346"/>
-    <cfRule type="duplicateValues" dxfId="355" priority="345"/>
-    <cfRule type="duplicateValues" dxfId="354" priority="344"/>
-    <cfRule type="duplicateValues" dxfId="353" priority="339"/>
-    <cfRule type="duplicateValues" dxfId="352" priority="338"/>
-    <cfRule type="duplicateValues" dxfId="351" priority="337"/>
+    <cfRule type="duplicateValues" dxfId="361" priority="344"/>
+    <cfRule type="duplicateValues" dxfId="360" priority="345"/>
+    <cfRule type="duplicateValues" dxfId="359" priority="346"/>
+    <cfRule type="duplicateValues" dxfId="358" priority="347"/>
+    <cfRule type="duplicateValues" dxfId="357" priority="348"/>
+    <cfRule type="duplicateValues" dxfId="356" priority="349"/>
+    <cfRule type="duplicateValues" dxfId="355" priority="350"/>
+    <cfRule type="duplicateValues" dxfId="354" priority="351"/>
+    <cfRule type="duplicateValues" dxfId="353" priority="352"/>
+    <cfRule type="duplicateValues" dxfId="352" priority="353"/>
+    <cfRule type="duplicateValues" dxfId="351" priority="354"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2442:D2673 D2:D18 D20:D2440 E19 D2677:D2692 D2697:D2698 D2701:D2708 D2711:D2729 D2731:D2733 D2737:D2752 D2755:D2757">
+  <conditionalFormatting sqref="F19 A2442:A2673 A2:A18 A20:A2440 A2677:A2692 A2697:A2698 A2701:A2708 A2711:A2729 A2731:A2733 A2737:A2752 A2755:A2757">
     <cfRule type="duplicateValues" dxfId="350" priority="355"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2442:D2673 D2393:D2428 D2:D18 D20:D2388 E19 D2433 D2436:D2440 D2677:D2692 D2697:D2698 D2701:D2708 D2711:D2729 D2731:D2733 D2737:D2752 D2755:D2757">
+  <conditionalFormatting sqref="F19 A2442:A2673 A2393:A2428 A2:A18 A20:A2388 A2433 A2436:A2440 A2677:A2692 A2697:A2698 A2701:A2708 A2711:A2729 A2731:A2733 A2737:A2752 A2755:A2757">
     <cfRule type="duplicateValues" dxfId="349" priority="502"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2442:D2673 D2393:D2428 D2273:D2341 D2209:D2213 D2198:D2207 D2182:D2193 D2:D18 D20:D889 E19 D963:D2180 D2221:D2223 D891:D961 D2229:D2265 D2345:D2346 D2348 D2350 D2353 D2358:D2363 D2365:D2371 D2374:D2388 D2433 D2436:D2440 D2677:D2692 D2697:D2698 D2701:D2708 D2711:D2729 D2731:D2733 D2737:D2752 D2755:D2757">
+  <conditionalFormatting sqref="F19 A2442:A2673 A2393:A2428 A2273:A2341 A2209:A2213 A2198:A2207 A2182:A2193 A2:A18 A20:A889 A963:A2180 A2221:A2223 A891:A961 A2229:A2265 A2345:A2346 A2348 A2350 A2353 A2358:A2363 A2365:A2371 A2374:A2388 A2433 A2436:A2440 A2677:A2692 A2697:A2698 A2701:A2708 A2711:A2729 A2731:A2733 A2737:A2752 A2755:A2757">
     <cfRule type="duplicateValues" dxfId="348" priority="1005"/>
     <cfRule type="duplicateValues" dxfId="347" priority="1006"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2442:D2673 D2393:D2428 D2273:D2341 D2209:D2213 D2198:D2207 D2182:D2193 D2148:D2150 D2:D18 D20:D889 E19 D2153:D2154 D2156:D2180 D963:D2142 D2221:D2223 D891:D961 D2229:D2265 D2345:D2346 D2348 D2350 D2353 D2358:D2363 D2365:D2371 D2374:D2388 D2433 D2436:D2440 D2677:D2692 D2697:D2698 D2701:D2708 D2711:D2729 D2731:D2733 D2737:D2752 D2755:D2757">
+  <conditionalFormatting sqref="F19 A2442:A2673 A2393:A2428 A2273:A2341 A2209:A2213 A2198:A2207 A2182:A2193 A2148:A2150 A2:A18 A20:A889 A2153:A2154 A2156:A2180 A963:A2142 A2221:A2223 A891:A961 A2229:A2265 A2345:A2346 A2348 A2350 A2353 A2358:A2363 A2365:A2371 A2374:A2388 A2433 A2436:A2440 A2677:A2692 A2697:A2698 A2701:A2708 A2711:A2729 A2731:A2733 A2737:A2752 A2755:A2757">
     <cfRule type="duplicateValues" dxfId="346" priority="1100"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2442:D2673 D2393:D2428 D2273:D2341 D2209:D2213 D2198:D2207 D2182:D2193 D2148:D2150 D2:D18 D20:D889 E19 D2153:D2154 D2156:D2180 D963:D2144 D2221:D2223 D891:D961 D2229:D2265 D2345:D2346 D2348 D2350 D2353 D2358:D2363 D2365:D2371 D2374:D2388 D2433 D2436:D2440 D2677:D2692 D2697:D2698 D2701:D2708 D2711:D2729 D2731:D2733 D2737:D2752 D2755:D2757">
+  <conditionalFormatting sqref="F19 A2442:A2673 A2393:A2428 A2273:A2341 A2209:A2213 A2198:A2207 A2182:A2193 A2148:A2150 A2:A18 A20:A889 A2153:A2154 A2156:A2180 A963:A2144 A2221:A2223 A891:A961 A2229:A2265 A2345:A2346 A2348 A2350 A2353 A2358:A2363 A2365:A2371 A2374:A2388 A2433 A2436:A2440 A2677:A2692 A2697:A2698 A2701:A2708 A2711:A2729 A2731:A2733 A2737:A2752 A2755:A2757">
     <cfRule type="duplicateValues" dxfId="345" priority="1085"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2442:D2673 D2393:D2428 D2273:D2341 D2209:D2213 D2198:D2207 D2182:D2193 D2148:D2150 D2117:D2142 D2:D18 D20:D889 E19 D2153:D2154 D2156:D2180 D963:D2115 D2221:D2223 D891:D961 D2229:D2265 D2345:D2346 D2348 D2350 D2353 D2358:D2363 D2365:D2371 D2374:D2388 D2433 D2436:D2440 D2677:D2692 D2697:D2698 D2701:D2708 D2711:D2729 D2731:D2733 D2737:D2752 D2755:D2757">
+  <conditionalFormatting sqref="F19 A2442:A2673 A2393:A2428 A2273:A2341 A2209:A2213 A2198:A2207 A2182:A2193 A2148:A2150 A2117:A2142 A2:A18 A20:A889 A2153:A2154 A2156:A2180 A963:A2115 A2221:A2223 A891:A961 A2229:A2265 A2345:A2346 A2348 A2350 A2353 A2358:A2363 A2365:A2371 A2374:A2388 A2433 A2436:A2440 A2677:A2692 A2697:A2698 A2701:A2708 A2711:A2729 A2731:A2733 A2737:A2752 A2755:A2757">
     <cfRule type="duplicateValues" dxfId="344" priority="1107"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2442:D2673 D2393:D2428 D2273:D2341 D2209:D2213 D2198:D2207 D2182:D2193 D2148:D2150 D2117:D2142 D2034 D1996:D1999 D2:D18 D20:D889 E19 D2001:D2002 D2004:D2013 D2015:D2017 D2019 D2021:D2032 D2036:D2058 D2062:D2078 D2081:D2082 D2089:D2091 D2093:D2099 D2102:D2115 D2153:D2154 D2156:D2180 D963:D1994 D2221:D2223 D891:D961 D2229:D2265 D2345:D2346 D2348 D2350 D2353 D2358:D2363 D2365:D2371 D2374:D2388 D2433 D2436:D2440 D2677:D2692 D2697:D2698 D2701:D2708 D2711:D2729 D2731:D2733 D2737:D2752 D2755:D2757">
+  <conditionalFormatting sqref="F19 A2442:A2673 A2393:A2428 A2273:A2341 A2209:A2213 A2198:A2207 A2182:A2193 A2148:A2150 A2117:A2142 A2034 A1996:A1999 A2:A18 A20:A889 A2001:A2002 A2004:A2013 A2015:A2017 A2019 A2021:A2032 A2036:A2058 A2062:A2078 A2081:A2082 A2089:A2091 A2093:A2099 A2102:A2115 A2153:A2154 A2156:A2180 A963:A1994 A2221:A2223 A891:A961 A2229:A2265 A2345:A2346 A2348 A2350 A2353 A2358:A2363 A2365:A2371 A2374:A2388 A2433 A2436:A2440 A2677:A2692 A2697:A2698 A2701:A2708 A2711:A2729 A2731:A2733 A2737:A2752 A2755:A2757">
     <cfRule type="duplicateValues" dxfId="343" priority="1188"/>
     <cfRule type="duplicateValues" dxfId="342" priority="1189"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2442:D2673 D2393:D2428 D2273:D2341 D2209:D2213 D2198:D2207 D2182:D2193 D2148:D2150 D2117:D2142 D2081:D2082 D2:D18 D20:D889 E19 D2089:D2091 D2093:D2099 D2102:D2115 D2153:D2154 D2156:D2180 D963:D2078 D2221:D2223 D891:D961 D2229:D2265 D2345:D2346 D2348 D2350 D2353 D2358:D2363 D2365:D2371 D2374:D2388 D2433 D2436:D2440 D2677:D2692 D2697:D2698 D2701:D2708 D2711:D2729 D2731:D2733 D2737:D2752 D2755:D2757">
+  <conditionalFormatting sqref="F19 A2442:A2673 A2393:A2428 A2273:A2341 A2209:A2213 A2198:A2207 A2182:A2193 A2148:A2150 A2117:A2142 A2081:A2082 A2:A18 A20:A889 A2089:A2091 A2093:A2099 A2102:A2115 A2153:A2154 A2156:A2180 A963:A2078 A2221:A2223 A891:A961 A2229:A2265 A2345:A2346 A2348 A2350 A2353 A2358:A2363 A2365:A2371 A2374:A2388 A2433 A2436:A2440 A2677:A2692 A2697:A2698 A2701:A2708 A2711:A2729 A2731:A2733 A2737:A2752 A2755:A2757">
     <cfRule type="duplicateValues" dxfId="341" priority="1163"/>
     <cfRule type="duplicateValues" dxfId="340" priority="1164"/>
     <cfRule type="duplicateValues" dxfId="339" priority="1165"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2442:D2673 D2393:D2428 D2273:D2341 D2209:D2213 D2198:D2207 D2182:D2193 D2156:D2180 D2:D18 D20:D889 E19 D963:D2154 D2221:D2223 D891:D961 D2229:D2265 D2345:D2346 D2348 D2350 D2353 D2358:D2363 D2365:D2371 D2374:D2388 D2433 D2436:D2440 D2677:D2692 D2697:D2698 D2701:D2708 D2711:D2729 D2731:D2733 D2737:D2752 D2755:D2757">
+  <conditionalFormatting sqref="F19 A2442:A2673 A2393:A2428 A2273:A2341 A2209:A2213 A2198:A2207 A2182:A2193 A2156:A2180 A2:A18 A20:A889 A963:A2154 A2221:A2223 A891:A961 A2229:A2265 A2345:A2346 A2348 A2350 A2353 A2358:A2363 A2365:A2371 A2374:A2388 A2433 A2436:A2440 A2677:A2692 A2697:A2698 A2701:A2708 A2711:A2729 A2731:A2733 A2737:A2752 A2755:A2757">
     <cfRule type="duplicateValues" dxfId="338" priority="1016"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2442:D2673 D2393:D2428 D2273:D2341 D2221:D2223 D2:D18 D20:D889 E19 D891:D2213 D2229:D2265 D2345:D2346 D2348 D2350 D2353 D2358:D2363 D2365:D2371 D2374:D2388 D2433 D2436:D2440 D2677:D2692 D2697:D2698 D2701:D2708 D2711:D2729 D2731:D2733 D2737:D2752 D2755:D2757">
+  <conditionalFormatting sqref="F19 A2442:A2673 A2393:A2428 A2273:A2341 A2221:A2223 A2:A18 A20:A889 A891:A2213 A2229:A2265 A2345:A2346 A2348 A2350 A2353 A2358:A2363 A2365:A2371 A2374:A2388 A2433 A2436:A2440 A2677:A2692 A2697:A2698 A2701:A2708 A2711:A2729 A2731:A2733 A2737:A2752 A2755:A2757">
     <cfRule type="duplicateValues" dxfId="337" priority="938"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2442:D2673 D2393:D2428 D2273:D2341 D2221:D2223 D2:D18 D20:D889 E19 D891:D2215 D2229:D2265 D2345:D2346 D2348 D2350 D2353 D2358:D2363 D2365:D2371 D2374:D2388 D2433 D2436:D2440 D2677:D2692 D2697:D2698 D2701:D2708 D2711:D2729 D2731:D2733 D2737:D2752 D2755:D2757">
+  <conditionalFormatting sqref="F19 A2442:A2673 A2393:A2428 A2273:A2341 A2221:A2223 A2:A18 A20:A889 A891:A2215 A2229:A2265 A2345:A2346 A2348 A2350 A2353 A2358:A2363 A2365:A2371 A2374:A2388 A2433 A2436:A2440 A2677:A2692 A2697:A2698 A2701:A2708 A2711:A2729 A2731:A2733 A2737:A2752 A2755:A2757">
     <cfRule type="duplicateValues" dxfId="336" priority="913"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2442:D2673 D2393:D2428 D2365:D2371 D2:D18 D20:D2363 E19 D2374:D2388 D2433 D2436:D2440 D2677:D2692 D2697:D2698 D2701:D2708 D2711:D2729 D2731:D2733 D2737:D2752 D2755:D2757">
+  <conditionalFormatting sqref="F19 A2442:A2673 A2393:A2428 A2365:A2371 A2:A18 A20:A2363 A2374:A2388 A2433 A2436:A2440 A2677:A2692 A2697:A2698 A2701:A2708 A2711:A2729 A2731:A2733 A2737:A2752 A2755:A2757">
     <cfRule type="duplicateValues" dxfId="335" priority="548"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2442:D2673 D2393:D2428 D2374:D2388 D2:D18 D20:D2371 E19 D2433 D2436:D2440 D2677:D2692 D2697:D2698 D2701:D2708 D2711:D2729 D2731:D2733 D2737:D2752 D2755:D2757">
+  <conditionalFormatting sqref="F19 A2442:A2673 A2393:A2428 A2374:A2388 A2:A18 A20:A2371 A2433 A2436:A2440 A2677:A2692 A2697:A2698 A2701:A2708 A2711:A2729 A2731:A2733 A2737:A2752 A2755:A2757">
     <cfRule type="duplicateValues" dxfId="334" priority="533"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2442:D2673 D2436:D2440 D2:D18 D20:D2434 E19 D2677:D2692 D2697:D2698 D2701:D2708 D2711:D2729 D2731:D2733 D2737:D2752 D2755:D2757">
+  <conditionalFormatting sqref="F19 A2442:A2673 A2436:A2440 A2:A18 A20:A2434 A2677:A2692 A2697:A2698 A2701:A2708 A2711:A2729 A2731:A2733 A2737:A2752 A2755:A2757">
     <cfRule type="duplicateValues" dxfId="333" priority="373"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2674">
-    <cfRule type="duplicateValues" dxfId="332" priority="325"/>
-    <cfRule type="duplicateValues" dxfId="331" priority="324"/>
-    <cfRule type="duplicateValues" dxfId="330" priority="323"/>
+  <conditionalFormatting sqref="A2674">
+    <cfRule type="duplicateValues" dxfId="332" priority="319"/>
+    <cfRule type="duplicateValues" dxfId="331" priority="320"/>
+    <cfRule type="duplicateValues" dxfId="330" priority="321"/>
     <cfRule type="duplicateValues" dxfId="329" priority="322"/>
-    <cfRule type="duplicateValues" dxfId="328" priority="321"/>
-    <cfRule type="duplicateValues" dxfId="327" priority="320"/>
-    <cfRule type="duplicateValues" dxfId="326" priority="319"/>
-    <cfRule type="duplicateValues" dxfId="325" priority="327"/>
-    <cfRule type="duplicateValues" dxfId="324" priority="336"/>
-    <cfRule type="duplicateValues" dxfId="323" priority="335"/>
-    <cfRule type="duplicateValues" dxfId="322" priority="334"/>
-    <cfRule type="duplicateValues" dxfId="321" priority="333"/>
-    <cfRule type="duplicateValues" dxfId="320" priority="332"/>
-    <cfRule type="duplicateValues" dxfId="319" priority="331"/>
-    <cfRule type="duplicateValues" dxfId="318" priority="330"/>
-    <cfRule type="duplicateValues" dxfId="317" priority="329"/>
-    <cfRule type="duplicateValues" dxfId="316" priority="328"/>
-    <cfRule type="duplicateValues" dxfId="315" priority="326"/>
+    <cfRule type="duplicateValues" dxfId="328" priority="323"/>
+    <cfRule type="duplicateValues" dxfId="327" priority="324"/>
+    <cfRule type="duplicateValues" dxfId="326" priority="325"/>
+    <cfRule type="duplicateValues" dxfId="325" priority="326"/>
+    <cfRule type="duplicateValues" dxfId="324" priority="327"/>
+    <cfRule type="duplicateValues" dxfId="323" priority="328"/>
+    <cfRule type="duplicateValues" dxfId="322" priority="329"/>
+    <cfRule type="duplicateValues" dxfId="321" priority="330"/>
+    <cfRule type="duplicateValues" dxfId="320" priority="331"/>
+    <cfRule type="duplicateValues" dxfId="319" priority="332"/>
+    <cfRule type="duplicateValues" dxfId="318" priority="333"/>
+    <cfRule type="duplicateValues" dxfId="317" priority="334"/>
+    <cfRule type="duplicateValues" dxfId="316" priority="335"/>
+    <cfRule type="duplicateValues" dxfId="315" priority="336"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2675">
-    <cfRule type="duplicateValues" dxfId="314" priority="307"/>
-    <cfRule type="duplicateValues" dxfId="313" priority="306"/>
-    <cfRule type="duplicateValues" dxfId="312" priority="305"/>
+  <conditionalFormatting sqref="A2675">
+    <cfRule type="duplicateValues" dxfId="314" priority="301"/>
+    <cfRule type="duplicateValues" dxfId="313" priority="302"/>
+    <cfRule type="duplicateValues" dxfId="312" priority="303"/>
     <cfRule type="duplicateValues" dxfId="311" priority="304"/>
-    <cfRule type="duplicateValues" dxfId="310" priority="303"/>
-    <cfRule type="duplicateValues" dxfId="309" priority="302"/>
-    <cfRule type="duplicateValues" dxfId="308" priority="301"/>
-    <cfRule type="duplicateValues" dxfId="307" priority="316"/>
-    <cfRule type="duplicateValues" dxfId="306" priority="308"/>
-    <cfRule type="duplicateValues" dxfId="305" priority="315"/>
-    <cfRule type="duplicateValues" dxfId="304" priority="314"/>
-    <cfRule type="duplicateValues" dxfId="303" priority="313"/>
-    <cfRule type="duplicateValues" dxfId="302" priority="312"/>
-    <cfRule type="duplicateValues" dxfId="301" priority="311"/>
-    <cfRule type="duplicateValues" dxfId="300" priority="310"/>
-    <cfRule type="duplicateValues" dxfId="299" priority="318"/>
+    <cfRule type="duplicateValues" dxfId="310" priority="305"/>
+    <cfRule type="duplicateValues" dxfId="309" priority="306"/>
+    <cfRule type="duplicateValues" dxfId="308" priority="307"/>
+    <cfRule type="duplicateValues" dxfId="307" priority="308"/>
+    <cfRule type="duplicateValues" dxfId="306" priority="309"/>
+    <cfRule type="duplicateValues" dxfId="305" priority="310"/>
+    <cfRule type="duplicateValues" dxfId="304" priority="311"/>
+    <cfRule type="duplicateValues" dxfId="303" priority="312"/>
+    <cfRule type="duplicateValues" dxfId="302" priority="313"/>
+    <cfRule type="duplicateValues" dxfId="301" priority="314"/>
+    <cfRule type="duplicateValues" dxfId="300" priority="315"/>
+    <cfRule type="duplicateValues" dxfId="299" priority="316"/>
     <cfRule type="duplicateValues" dxfId="298" priority="317"/>
-    <cfRule type="duplicateValues" dxfId="297" priority="309"/>
+    <cfRule type="duplicateValues" dxfId="297" priority="318"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2676">
-    <cfRule type="duplicateValues" dxfId="296" priority="289"/>
-    <cfRule type="duplicateValues" dxfId="295" priority="288"/>
-    <cfRule type="duplicateValues" dxfId="294" priority="287"/>
+  <conditionalFormatting sqref="A2676">
+    <cfRule type="duplicateValues" dxfId="296" priority="283"/>
+    <cfRule type="duplicateValues" dxfId="295" priority="284"/>
+    <cfRule type="duplicateValues" dxfId="294" priority="285"/>
     <cfRule type="duplicateValues" dxfId="293" priority="286"/>
-    <cfRule type="duplicateValues" dxfId="292" priority="285"/>
-    <cfRule type="duplicateValues" dxfId="291" priority="284"/>
-    <cfRule type="duplicateValues" dxfId="290" priority="283"/>
-    <cfRule type="duplicateValues" dxfId="289" priority="300"/>
-    <cfRule type="duplicateValues" dxfId="288" priority="298"/>
-    <cfRule type="duplicateValues" dxfId="287" priority="299"/>
-    <cfRule type="duplicateValues" dxfId="286" priority="297"/>
-    <cfRule type="duplicateValues" dxfId="285" priority="296"/>
+    <cfRule type="duplicateValues" dxfId="292" priority="287"/>
+    <cfRule type="duplicateValues" dxfId="291" priority="288"/>
+    <cfRule type="duplicateValues" dxfId="290" priority="289"/>
+    <cfRule type="duplicateValues" dxfId="289" priority="290"/>
+    <cfRule type="duplicateValues" dxfId="288" priority="291"/>
+    <cfRule type="duplicateValues" dxfId="287" priority="292"/>
+    <cfRule type="duplicateValues" dxfId="286" priority="293"/>
+    <cfRule type="duplicateValues" dxfId="285" priority="294"/>
     <cfRule type="duplicateValues" dxfId="284" priority="295"/>
-    <cfRule type="duplicateValues" dxfId="283" priority="294"/>
-    <cfRule type="duplicateValues" dxfId="282" priority="293"/>
-    <cfRule type="duplicateValues" dxfId="281" priority="292"/>
-    <cfRule type="duplicateValues" dxfId="280" priority="291"/>
-    <cfRule type="duplicateValues" dxfId="279" priority="290"/>
+    <cfRule type="duplicateValues" dxfId="283" priority="296"/>
+    <cfRule type="duplicateValues" dxfId="282" priority="297"/>
+    <cfRule type="duplicateValues" dxfId="281" priority="298"/>
+    <cfRule type="duplicateValues" dxfId="280" priority="299"/>
+    <cfRule type="duplicateValues" dxfId="279" priority="300"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2693">
-    <cfRule type="duplicateValues" dxfId="278" priority="272"/>
-    <cfRule type="duplicateValues" dxfId="277" priority="271"/>
-    <cfRule type="duplicateValues" dxfId="276" priority="270"/>
-    <cfRule type="duplicateValues" dxfId="275" priority="269"/>
-    <cfRule type="duplicateValues" dxfId="274" priority="268"/>
-    <cfRule type="duplicateValues" dxfId="273" priority="267"/>
-    <cfRule type="duplicateValues" dxfId="272" priority="266"/>
-    <cfRule type="duplicateValues" dxfId="271" priority="265"/>
-    <cfRule type="duplicateValues" dxfId="270" priority="278"/>
+  <conditionalFormatting sqref="A2693">
+    <cfRule type="duplicateValues" dxfId="278" priority="265"/>
+    <cfRule type="duplicateValues" dxfId="277" priority="266"/>
+    <cfRule type="duplicateValues" dxfId="276" priority="267"/>
+    <cfRule type="duplicateValues" dxfId="275" priority="268"/>
+    <cfRule type="duplicateValues" dxfId="274" priority="269"/>
+    <cfRule type="duplicateValues" dxfId="273" priority="270"/>
+    <cfRule type="duplicateValues" dxfId="272" priority="271"/>
+    <cfRule type="duplicateValues" dxfId="271" priority="272"/>
+    <cfRule type="duplicateValues" dxfId="270" priority="273"/>
     <cfRule type="duplicateValues" dxfId="269" priority="274"/>
-    <cfRule type="duplicateValues" dxfId="268" priority="282"/>
-    <cfRule type="duplicateValues" dxfId="267" priority="275"/>
+    <cfRule type="duplicateValues" dxfId="268" priority="275"/>
+    <cfRule type="duplicateValues" dxfId="267" priority="276"/>
     <cfRule type="duplicateValues" dxfId="266" priority="277"/>
-    <cfRule type="duplicateValues" dxfId="265" priority="276"/>
+    <cfRule type="duplicateValues" dxfId="265" priority="278"/>
     <cfRule type="duplicateValues" dxfId="264" priority="279"/>
     <cfRule type="duplicateValues" dxfId="263" priority="280"/>
-    <cfRule type="duplicateValues" dxfId="262" priority="273"/>
-    <cfRule type="duplicateValues" dxfId="261" priority="281"/>
+    <cfRule type="duplicateValues" dxfId="262" priority="281"/>
+    <cfRule type="duplicateValues" dxfId="261" priority="282"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2694">
-    <cfRule type="duplicateValues" dxfId="260" priority="264"/>
-    <cfRule type="duplicateValues" dxfId="259" priority="262"/>
-    <cfRule type="duplicateValues" dxfId="258" priority="261"/>
-    <cfRule type="duplicateValues" dxfId="257" priority="260"/>
-    <cfRule type="duplicateValues" dxfId="256" priority="259"/>
-    <cfRule type="duplicateValues" dxfId="255" priority="258"/>
-    <cfRule type="duplicateValues" dxfId="254" priority="257"/>
-    <cfRule type="duplicateValues" dxfId="253" priority="256"/>
+  <conditionalFormatting sqref="A2694">
+    <cfRule type="duplicateValues" dxfId="260" priority="247"/>
+    <cfRule type="duplicateValues" dxfId="259" priority="248"/>
+    <cfRule type="duplicateValues" dxfId="258" priority="249"/>
+    <cfRule type="duplicateValues" dxfId="257" priority="250"/>
+    <cfRule type="duplicateValues" dxfId="256" priority="251"/>
+    <cfRule type="duplicateValues" dxfId="255" priority="252"/>
+    <cfRule type="duplicateValues" dxfId="254" priority="253"/>
+    <cfRule type="duplicateValues" dxfId="253" priority="254"/>
     <cfRule type="duplicateValues" dxfId="252" priority="255"/>
-    <cfRule type="duplicateValues" dxfId="251" priority="254"/>
-    <cfRule type="duplicateValues" dxfId="250" priority="253"/>
-    <cfRule type="duplicateValues" dxfId="249" priority="252"/>
-    <cfRule type="duplicateValues" dxfId="248" priority="251"/>
-    <cfRule type="duplicateValues" dxfId="247" priority="250"/>
-    <cfRule type="duplicateValues" dxfId="246" priority="249"/>
-    <cfRule type="duplicateValues" dxfId="245" priority="248"/>
-    <cfRule type="duplicateValues" dxfId="244" priority="247"/>
-    <cfRule type="duplicateValues" dxfId="243" priority="263"/>
+    <cfRule type="duplicateValues" dxfId="251" priority="256"/>
+    <cfRule type="duplicateValues" dxfId="250" priority="257"/>
+    <cfRule type="duplicateValues" dxfId="249" priority="258"/>
+    <cfRule type="duplicateValues" dxfId="248" priority="259"/>
+    <cfRule type="duplicateValues" dxfId="247" priority="260"/>
+    <cfRule type="duplicateValues" dxfId="246" priority="261"/>
+    <cfRule type="duplicateValues" dxfId="245" priority="262"/>
+    <cfRule type="duplicateValues" dxfId="244" priority="263"/>
+    <cfRule type="duplicateValues" dxfId="243" priority="264"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2695">
-    <cfRule type="duplicateValues" dxfId="242" priority="245"/>
-    <cfRule type="duplicateValues" dxfId="241" priority="236"/>
-    <cfRule type="duplicateValues" dxfId="240" priority="235"/>
-    <cfRule type="duplicateValues" dxfId="239" priority="234"/>
+  <conditionalFormatting sqref="A2695">
+    <cfRule type="duplicateValues" dxfId="242" priority="229"/>
+    <cfRule type="duplicateValues" dxfId="241" priority="230"/>
+    <cfRule type="duplicateValues" dxfId="240" priority="231"/>
+    <cfRule type="duplicateValues" dxfId="239" priority="232"/>
     <cfRule type="duplicateValues" dxfId="238" priority="233"/>
-    <cfRule type="duplicateValues" dxfId="237" priority="232"/>
-    <cfRule type="duplicateValues" dxfId="236" priority="231"/>
-    <cfRule type="duplicateValues" dxfId="235" priority="230"/>
-    <cfRule type="duplicateValues" dxfId="234" priority="229"/>
-    <cfRule type="duplicateValues" dxfId="233" priority="237"/>
-    <cfRule type="duplicateValues" dxfId="232" priority="238"/>
-    <cfRule type="duplicateValues" dxfId="231" priority="246"/>
-    <cfRule type="duplicateValues" dxfId="230" priority="239"/>
-    <cfRule type="duplicateValues" dxfId="229" priority="240"/>
-    <cfRule type="duplicateValues" dxfId="228" priority="241"/>
-    <cfRule type="duplicateValues" dxfId="227" priority="242"/>
-    <cfRule type="duplicateValues" dxfId="226" priority="243"/>
-    <cfRule type="duplicateValues" dxfId="225" priority="244"/>
+    <cfRule type="duplicateValues" dxfId="237" priority="234"/>
+    <cfRule type="duplicateValues" dxfId="236" priority="235"/>
+    <cfRule type="duplicateValues" dxfId="235" priority="236"/>
+    <cfRule type="duplicateValues" dxfId="234" priority="237"/>
+    <cfRule type="duplicateValues" dxfId="233" priority="238"/>
+    <cfRule type="duplicateValues" dxfId="232" priority="239"/>
+    <cfRule type="duplicateValues" dxfId="231" priority="240"/>
+    <cfRule type="duplicateValues" dxfId="230" priority="241"/>
+    <cfRule type="duplicateValues" dxfId="229" priority="242"/>
+    <cfRule type="duplicateValues" dxfId="228" priority="243"/>
+    <cfRule type="duplicateValues" dxfId="227" priority="244"/>
+    <cfRule type="duplicateValues" dxfId="226" priority="245"/>
+    <cfRule type="duplicateValues" dxfId="225" priority="246"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2696">
-    <cfRule type="duplicateValues" dxfId="224" priority="185"/>
-    <cfRule type="duplicateValues" dxfId="223" priority="184"/>
-    <cfRule type="duplicateValues" dxfId="222" priority="183"/>
-    <cfRule type="duplicateValues" dxfId="221" priority="182"/>
-    <cfRule type="duplicateValues" dxfId="220" priority="181"/>
+  <conditionalFormatting sqref="A2696">
+    <cfRule type="duplicateValues" dxfId="224" priority="175"/>
+    <cfRule type="duplicateValues" dxfId="223" priority="176"/>
+    <cfRule type="duplicateValues" dxfId="222" priority="177"/>
+    <cfRule type="duplicateValues" dxfId="221" priority="178"/>
+    <cfRule type="duplicateValues" dxfId="220" priority="179"/>
     <cfRule type="duplicateValues" dxfId="219" priority="180"/>
-    <cfRule type="duplicateValues" dxfId="218" priority="179"/>
-    <cfRule type="duplicateValues" dxfId="217" priority="178"/>
-    <cfRule type="duplicateValues" dxfId="216" priority="186"/>
-    <cfRule type="duplicateValues" dxfId="215" priority="187"/>
-    <cfRule type="duplicateValues" dxfId="214" priority="176"/>
-    <cfRule type="duplicateValues" dxfId="213" priority="175"/>
-    <cfRule type="duplicateValues" dxfId="212" priority="188"/>
-    <cfRule type="duplicateValues" dxfId="211" priority="189"/>
-    <cfRule type="duplicateValues" dxfId="210" priority="190"/>
-    <cfRule type="duplicateValues" dxfId="209" priority="191"/>
-    <cfRule type="duplicateValues" dxfId="208" priority="192"/>
-    <cfRule type="duplicateValues" dxfId="207" priority="177"/>
+    <cfRule type="duplicateValues" dxfId="218" priority="181"/>
+    <cfRule type="duplicateValues" dxfId="217" priority="182"/>
+    <cfRule type="duplicateValues" dxfId="216" priority="183"/>
+    <cfRule type="duplicateValues" dxfId="215" priority="184"/>
+    <cfRule type="duplicateValues" dxfId="214" priority="185"/>
+    <cfRule type="duplicateValues" dxfId="213" priority="186"/>
+    <cfRule type="duplicateValues" dxfId="212" priority="187"/>
+    <cfRule type="duplicateValues" dxfId="211" priority="188"/>
+    <cfRule type="duplicateValues" dxfId="210" priority="189"/>
+    <cfRule type="duplicateValues" dxfId="209" priority="190"/>
+    <cfRule type="duplicateValues" dxfId="208" priority="191"/>
+    <cfRule type="duplicateValues" dxfId="207" priority="192"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2699">
-    <cfRule type="duplicateValues" dxfId="206" priority="219"/>
-    <cfRule type="duplicateValues" dxfId="205" priority="228"/>
-    <cfRule type="duplicateValues" dxfId="204" priority="227"/>
-    <cfRule type="duplicateValues" dxfId="203" priority="226"/>
-    <cfRule type="duplicateValues" dxfId="202" priority="225"/>
-    <cfRule type="duplicateValues" dxfId="201" priority="224"/>
-    <cfRule type="duplicateValues" dxfId="200" priority="223"/>
-    <cfRule type="duplicateValues" dxfId="199" priority="222"/>
-    <cfRule type="duplicateValues" dxfId="198" priority="221"/>
+  <conditionalFormatting sqref="A2699">
+    <cfRule type="duplicateValues" dxfId="206" priority="211"/>
+    <cfRule type="duplicateValues" dxfId="205" priority="212"/>
+    <cfRule type="duplicateValues" dxfId="204" priority="213"/>
+    <cfRule type="duplicateValues" dxfId="203" priority="214"/>
+    <cfRule type="duplicateValues" dxfId="202" priority="215"/>
+    <cfRule type="duplicateValues" dxfId="201" priority="216"/>
+    <cfRule type="duplicateValues" dxfId="200" priority="217"/>
+    <cfRule type="duplicateValues" dxfId="199" priority="218"/>
+    <cfRule type="duplicateValues" dxfId="198" priority="219"/>
     <cfRule type="duplicateValues" dxfId="197" priority="220"/>
-    <cfRule type="duplicateValues" dxfId="196" priority="218"/>
-    <cfRule type="duplicateValues" dxfId="195" priority="217"/>
-    <cfRule type="duplicateValues" dxfId="194" priority="216"/>
-    <cfRule type="duplicateValues" dxfId="193" priority="215"/>
-    <cfRule type="duplicateValues" dxfId="192" priority="214"/>
-    <cfRule type="duplicateValues" dxfId="191" priority="213"/>
-    <cfRule type="duplicateValues" dxfId="190" priority="212"/>
-    <cfRule type="duplicateValues" dxfId="189" priority="211"/>
+    <cfRule type="duplicateValues" dxfId="196" priority="221"/>
+    <cfRule type="duplicateValues" dxfId="195" priority="222"/>
+    <cfRule type="duplicateValues" dxfId="194" priority="223"/>
+    <cfRule type="duplicateValues" dxfId="193" priority="224"/>
+    <cfRule type="duplicateValues" dxfId="192" priority="225"/>
+    <cfRule type="duplicateValues" dxfId="191" priority="226"/>
+    <cfRule type="duplicateValues" dxfId="190" priority="227"/>
+    <cfRule type="duplicateValues" dxfId="189" priority="228"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2700">
-    <cfRule type="duplicateValues" dxfId="188" priority="201"/>
-    <cfRule type="duplicateValues" dxfId="187" priority="200"/>
-    <cfRule type="duplicateValues" dxfId="186" priority="199"/>
-    <cfRule type="duplicateValues" dxfId="185" priority="198"/>
+  <conditionalFormatting sqref="A2700">
+    <cfRule type="duplicateValues" dxfId="188" priority="193"/>
+    <cfRule type="duplicateValues" dxfId="187" priority="194"/>
+    <cfRule type="duplicateValues" dxfId="186" priority="195"/>
+    <cfRule type="duplicateValues" dxfId="185" priority="196"/>
     <cfRule type="duplicateValues" dxfId="184" priority="197"/>
-    <cfRule type="duplicateValues" dxfId="183" priority="196"/>
-    <cfRule type="duplicateValues" dxfId="182" priority="195"/>
-    <cfRule type="duplicateValues" dxfId="181" priority="194"/>
-    <cfRule type="duplicateValues" dxfId="180" priority="193"/>
+    <cfRule type="duplicateValues" dxfId="183" priority="198"/>
+    <cfRule type="duplicateValues" dxfId="182" priority="199"/>
+    <cfRule type="duplicateValues" dxfId="181" priority="200"/>
+    <cfRule type="duplicateValues" dxfId="180" priority="201"/>
     <cfRule type="duplicateValues" dxfId="179" priority="202"/>
     <cfRule type="duplicateValues" dxfId="178" priority="203"/>
     <cfRule type="duplicateValues" dxfId="177" priority="204"/>
@@ -13728,196 +13741,196 @@
     <cfRule type="duplicateValues" dxfId="172" priority="209"/>
     <cfRule type="duplicateValues" dxfId="171" priority="210"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2709">
-    <cfRule type="duplicateValues" dxfId="170" priority="168"/>
-    <cfRule type="duplicateValues" dxfId="169" priority="167"/>
-    <cfRule type="duplicateValues" dxfId="168" priority="166"/>
-    <cfRule type="duplicateValues" dxfId="167" priority="165"/>
-    <cfRule type="duplicateValues" dxfId="166" priority="164"/>
-    <cfRule type="duplicateValues" dxfId="165" priority="163"/>
-    <cfRule type="duplicateValues" dxfId="164" priority="162"/>
-    <cfRule type="duplicateValues" dxfId="163" priority="161"/>
-    <cfRule type="duplicateValues" dxfId="162" priority="160"/>
-    <cfRule type="duplicateValues" dxfId="161" priority="159"/>
-    <cfRule type="duplicateValues" dxfId="160" priority="158"/>
-    <cfRule type="duplicateValues" dxfId="159" priority="157"/>
+  <conditionalFormatting sqref="A2709">
+    <cfRule type="duplicateValues" dxfId="170" priority="157"/>
+    <cfRule type="duplicateValues" dxfId="169" priority="158"/>
+    <cfRule type="duplicateValues" dxfId="168" priority="159"/>
+    <cfRule type="duplicateValues" dxfId="167" priority="160"/>
+    <cfRule type="duplicateValues" dxfId="166" priority="161"/>
+    <cfRule type="duplicateValues" dxfId="165" priority="162"/>
+    <cfRule type="duplicateValues" dxfId="164" priority="163"/>
+    <cfRule type="duplicateValues" dxfId="163" priority="164"/>
+    <cfRule type="duplicateValues" dxfId="162" priority="165"/>
+    <cfRule type="duplicateValues" dxfId="161" priority="166"/>
+    <cfRule type="duplicateValues" dxfId="160" priority="167"/>
+    <cfRule type="duplicateValues" dxfId="159" priority="168"/>
     <cfRule type="duplicateValues" dxfId="158" priority="169"/>
-    <cfRule type="duplicateValues" dxfId="157" priority="174"/>
-    <cfRule type="duplicateValues" dxfId="156" priority="173"/>
+    <cfRule type="duplicateValues" dxfId="157" priority="170"/>
+    <cfRule type="duplicateValues" dxfId="156" priority="171"/>
     <cfRule type="duplicateValues" dxfId="155" priority="172"/>
-    <cfRule type="duplicateValues" dxfId="154" priority="171"/>
-    <cfRule type="duplicateValues" dxfId="153" priority="170"/>
+    <cfRule type="duplicateValues" dxfId="154" priority="173"/>
+    <cfRule type="duplicateValues" dxfId="153" priority="174"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2710">
-    <cfRule type="duplicateValues" dxfId="152" priority="149"/>
-    <cfRule type="duplicateValues" dxfId="151" priority="148"/>
-    <cfRule type="duplicateValues" dxfId="150" priority="147"/>
-    <cfRule type="duplicateValues" dxfId="149" priority="155"/>
-    <cfRule type="duplicateValues" dxfId="148" priority="146"/>
-    <cfRule type="duplicateValues" dxfId="147" priority="145"/>
-    <cfRule type="duplicateValues" dxfId="146" priority="144"/>
-    <cfRule type="duplicateValues" dxfId="145" priority="143"/>
-    <cfRule type="duplicateValues" dxfId="144" priority="142"/>
-    <cfRule type="duplicateValues" dxfId="143" priority="141"/>
-    <cfRule type="duplicateValues" dxfId="142" priority="140"/>
-    <cfRule type="duplicateValues" dxfId="141" priority="139"/>
-    <cfRule type="duplicateValues" dxfId="140" priority="154"/>
-    <cfRule type="duplicateValues" dxfId="139" priority="153"/>
-    <cfRule type="duplicateValues" dxfId="138" priority="150"/>
-    <cfRule type="duplicateValues" dxfId="137" priority="152"/>
-    <cfRule type="duplicateValues" dxfId="136" priority="156"/>
-    <cfRule type="duplicateValues" dxfId="135" priority="151"/>
+  <conditionalFormatting sqref="A2710">
+    <cfRule type="duplicateValues" dxfId="152" priority="139"/>
+    <cfRule type="duplicateValues" dxfId="151" priority="140"/>
+    <cfRule type="duplicateValues" dxfId="150" priority="141"/>
+    <cfRule type="duplicateValues" dxfId="149" priority="142"/>
+    <cfRule type="duplicateValues" dxfId="148" priority="143"/>
+    <cfRule type="duplicateValues" dxfId="147" priority="144"/>
+    <cfRule type="duplicateValues" dxfId="146" priority="145"/>
+    <cfRule type="duplicateValues" dxfId="145" priority="146"/>
+    <cfRule type="duplicateValues" dxfId="144" priority="147"/>
+    <cfRule type="duplicateValues" dxfId="143" priority="148"/>
+    <cfRule type="duplicateValues" dxfId="142" priority="149"/>
+    <cfRule type="duplicateValues" dxfId="141" priority="150"/>
+    <cfRule type="duplicateValues" dxfId="140" priority="151"/>
+    <cfRule type="duplicateValues" dxfId="139" priority="152"/>
+    <cfRule type="duplicateValues" dxfId="138" priority="153"/>
+    <cfRule type="duplicateValues" dxfId="137" priority="154"/>
+    <cfRule type="duplicateValues" dxfId="136" priority="155"/>
+    <cfRule type="duplicateValues" dxfId="135" priority="156"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2730">
-    <cfRule type="duplicateValues" dxfId="134" priority="132"/>
-    <cfRule type="duplicateValues" dxfId="133" priority="131"/>
-    <cfRule type="duplicateValues" dxfId="132" priority="130"/>
-    <cfRule type="duplicateValues" dxfId="131" priority="129"/>
-    <cfRule type="duplicateValues" dxfId="130" priority="128"/>
-    <cfRule type="duplicateValues" dxfId="129" priority="127"/>
-    <cfRule type="duplicateValues" dxfId="128" priority="126"/>
-    <cfRule type="duplicateValues" dxfId="127" priority="125"/>
-    <cfRule type="duplicateValues" dxfId="126" priority="124"/>
-    <cfRule type="duplicateValues" dxfId="125" priority="123"/>
-    <cfRule type="duplicateValues" dxfId="124" priority="122"/>
-    <cfRule type="duplicateValues" dxfId="123" priority="121"/>
-    <cfRule type="duplicateValues" dxfId="122" priority="120"/>
-    <cfRule type="duplicateValues" dxfId="121" priority="119"/>
-    <cfRule type="duplicateValues" dxfId="120" priority="137"/>
-    <cfRule type="duplicateValues" dxfId="119" priority="136"/>
+  <conditionalFormatting sqref="A2730">
+    <cfRule type="duplicateValues" dxfId="134" priority="119"/>
+    <cfRule type="duplicateValues" dxfId="133" priority="120"/>
+    <cfRule type="duplicateValues" dxfId="132" priority="121"/>
+    <cfRule type="duplicateValues" dxfId="131" priority="122"/>
+    <cfRule type="duplicateValues" dxfId="130" priority="123"/>
+    <cfRule type="duplicateValues" dxfId="129" priority="124"/>
+    <cfRule type="duplicateValues" dxfId="128" priority="125"/>
+    <cfRule type="duplicateValues" dxfId="127" priority="126"/>
+    <cfRule type="duplicateValues" dxfId="126" priority="127"/>
+    <cfRule type="duplicateValues" dxfId="125" priority="128"/>
+    <cfRule type="duplicateValues" dxfId="124" priority="129"/>
+    <cfRule type="duplicateValues" dxfId="123" priority="130"/>
+    <cfRule type="duplicateValues" dxfId="122" priority="131"/>
+    <cfRule type="duplicateValues" dxfId="121" priority="132"/>
+    <cfRule type="duplicateValues" dxfId="120" priority="133"/>
+    <cfRule type="duplicateValues" dxfId="119" priority="134"/>
     <cfRule type="duplicateValues" dxfId="118" priority="135"/>
-    <cfRule type="duplicateValues" dxfId="117" priority="134"/>
-    <cfRule type="duplicateValues" dxfId="116" priority="133"/>
+    <cfRule type="duplicateValues" dxfId="117" priority="136"/>
+    <cfRule type="duplicateValues" dxfId="116" priority="137"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2731:D2733 D2:D18 D20:D2729 E19 D2737:D2752 D2755:D2757">
+  <conditionalFormatting sqref="F19 A2731:A2733 A2:A18 A20:A2729 A2737:A2752 A2755:A2757">
     <cfRule type="duplicateValues" dxfId="115" priority="138"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2734">
-    <cfRule type="duplicateValues" dxfId="114" priority="113"/>
-    <cfRule type="duplicateValues" dxfId="113" priority="112"/>
-    <cfRule type="duplicateValues" dxfId="112" priority="111"/>
-    <cfRule type="duplicateValues" dxfId="111" priority="110"/>
-    <cfRule type="duplicateValues" dxfId="110" priority="109"/>
-    <cfRule type="duplicateValues" dxfId="109" priority="108"/>
-    <cfRule type="duplicateValues" dxfId="108" priority="107"/>
-    <cfRule type="duplicateValues" dxfId="107" priority="106"/>
-    <cfRule type="duplicateValues" dxfId="106" priority="105"/>
-    <cfRule type="duplicateValues" dxfId="105" priority="104"/>
-    <cfRule type="duplicateValues" dxfId="104" priority="103"/>
-    <cfRule type="duplicateValues" dxfId="103" priority="102"/>
-    <cfRule type="duplicateValues" dxfId="102" priority="101"/>
-    <cfRule type="duplicateValues" dxfId="101" priority="100"/>
-    <cfRule type="duplicateValues" dxfId="100" priority="118"/>
-    <cfRule type="duplicateValues" dxfId="99" priority="117"/>
-    <cfRule type="duplicateValues" dxfId="98" priority="114"/>
-    <cfRule type="duplicateValues" dxfId="97" priority="116"/>
-    <cfRule type="duplicateValues" dxfId="96" priority="115"/>
+  <conditionalFormatting sqref="A2734">
+    <cfRule type="duplicateValues" dxfId="114" priority="100"/>
+    <cfRule type="duplicateValues" dxfId="113" priority="101"/>
+    <cfRule type="duplicateValues" dxfId="112" priority="102"/>
+    <cfRule type="duplicateValues" dxfId="111" priority="103"/>
+    <cfRule type="duplicateValues" dxfId="110" priority="104"/>
+    <cfRule type="duplicateValues" dxfId="109" priority="105"/>
+    <cfRule type="duplicateValues" dxfId="108" priority="106"/>
+    <cfRule type="duplicateValues" dxfId="107" priority="107"/>
+    <cfRule type="duplicateValues" dxfId="106" priority="108"/>
+    <cfRule type="duplicateValues" dxfId="105" priority="109"/>
+    <cfRule type="duplicateValues" dxfId="104" priority="110"/>
+    <cfRule type="duplicateValues" dxfId="103" priority="111"/>
+    <cfRule type="duplicateValues" dxfId="102" priority="112"/>
+    <cfRule type="duplicateValues" dxfId="101" priority="113"/>
+    <cfRule type="duplicateValues" dxfId="100" priority="114"/>
+    <cfRule type="duplicateValues" dxfId="99" priority="115"/>
+    <cfRule type="duplicateValues" dxfId="98" priority="116"/>
+    <cfRule type="duplicateValues" dxfId="97" priority="117"/>
+    <cfRule type="duplicateValues" dxfId="96" priority="118"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2735">
-    <cfRule type="duplicateValues" dxfId="95" priority="96"/>
-    <cfRule type="duplicateValues" dxfId="94" priority="95"/>
-    <cfRule type="duplicateValues" dxfId="93" priority="94"/>
-    <cfRule type="duplicateValues" dxfId="92" priority="93"/>
-    <cfRule type="duplicateValues" dxfId="91" priority="92"/>
-    <cfRule type="duplicateValues" dxfId="90" priority="91"/>
-    <cfRule type="duplicateValues" dxfId="89" priority="90"/>
-    <cfRule type="duplicateValues" dxfId="88" priority="89"/>
-    <cfRule type="duplicateValues" dxfId="87" priority="88"/>
-    <cfRule type="duplicateValues" dxfId="86" priority="87"/>
-    <cfRule type="duplicateValues" dxfId="85" priority="86"/>
-    <cfRule type="duplicateValues" dxfId="84" priority="85"/>
-    <cfRule type="duplicateValues" dxfId="83" priority="84"/>
-    <cfRule type="duplicateValues" dxfId="82" priority="83"/>
-    <cfRule type="duplicateValues" dxfId="81" priority="82"/>
-    <cfRule type="duplicateValues" dxfId="80" priority="81"/>
-    <cfRule type="duplicateValues" dxfId="79" priority="99"/>
+  <conditionalFormatting sqref="A2735">
+    <cfRule type="duplicateValues" dxfId="95" priority="81"/>
+    <cfRule type="duplicateValues" dxfId="94" priority="82"/>
+    <cfRule type="duplicateValues" dxfId="93" priority="83"/>
+    <cfRule type="duplicateValues" dxfId="92" priority="84"/>
+    <cfRule type="duplicateValues" dxfId="91" priority="85"/>
+    <cfRule type="duplicateValues" dxfId="90" priority="86"/>
+    <cfRule type="duplicateValues" dxfId="89" priority="87"/>
+    <cfRule type="duplicateValues" dxfId="88" priority="88"/>
+    <cfRule type="duplicateValues" dxfId="87" priority="89"/>
+    <cfRule type="duplicateValues" dxfId="86" priority="90"/>
+    <cfRule type="duplicateValues" dxfId="85" priority="91"/>
+    <cfRule type="duplicateValues" dxfId="84" priority="92"/>
+    <cfRule type="duplicateValues" dxfId="83" priority="93"/>
+    <cfRule type="duplicateValues" dxfId="82" priority="94"/>
+    <cfRule type="duplicateValues" dxfId="81" priority="95"/>
+    <cfRule type="duplicateValues" dxfId="80" priority="96"/>
+    <cfRule type="duplicateValues" dxfId="79" priority="97"/>
     <cfRule type="duplicateValues" dxfId="78" priority="98"/>
-    <cfRule type="duplicateValues" dxfId="77" priority="97"/>
+    <cfRule type="duplicateValues" dxfId="77" priority="99"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2736">
-    <cfRule type="duplicateValues" dxfId="76" priority="77"/>
-    <cfRule type="duplicateValues" dxfId="75" priority="76"/>
-    <cfRule type="duplicateValues" dxfId="74" priority="75"/>
-    <cfRule type="duplicateValues" dxfId="73" priority="74"/>
-    <cfRule type="duplicateValues" dxfId="72" priority="80"/>
-    <cfRule type="duplicateValues" dxfId="71" priority="72"/>
-    <cfRule type="duplicateValues" dxfId="70" priority="71"/>
-    <cfRule type="duplicateValues" dxfId="69" priority="70"/>
-    <cfRule type="duplicateValues" dxfId="68" priority="69"/>
-    <cfRule type="duplicateValues" dxfId="67" priority="68"/>
-    <cfRule type="duplicateValues" dxfId="66" priority="67"/>
+  <conditionalFormatting sqref="A2736">
+    <cfRule type="duplicateValues" dxfId="76" priority="62"/>
+    <cfRule type="duplicateValues" dxfId="75" priority="63"/>
+    <cfRule type="duplicateValues" dxfId="74" priority="64"/>
+    <cfRule type="duplicateValues" dxfId="73" priority="65"/>
+    <cfRule type="duplicateValues" dxfId="72" priority="66"/>
+    <cfRule type="duplicateValues" dxfId="71" priority="67"/>
+    <cfRule type="duplicateValues" dxfId="70" priority="68"/>
+    <cfRule type="duplicateValues" dxfId="69" priority="69"/>
+    <cfRule type="duplicateValues" dxfId="68" priority="70"/>
+    <cfRule type="duplicateValues" dxfId="67" priority="71"/>
+    <cfRule type="duplicateValues" dxfId="66" priority="72"/>
     <cfRule type="duplicateValues" dxfId="65" priority="73"/>
-    <cfRule type="duplicateValues" dxfId="64" priority="65"/>
-    <cfRule type="duplicateValues" dxfId="63" priority="64"/>
-    <cfRule type="duplicateValues" dxfId="62" priority="63"/>
-    <cfRule type="duplicateValues" dxfId="61" priority="62"/>
-    <cfRule type="duplicateValues" dxfId="60" priority="79"/>
-    <cfRule type="duplicateValues" dxfId="59" priority="78"/>
-    <cfRule type="duplicateValues" dxfId="58" priority="66"/>
+    <cfRule type="duplicateValues" dxfId="64" priority="74"/>
+    <cfRule type="duplicateValues" dxfId="63" priority="75"/>
+    <cfRule type="duplicateValues" dxfId="62" priority="76"/>
+    <cfRule type="duplicateValues" dxfId="61" priority="77"/>
+    <cfRule type="duplicateValues" dxfId="60" priority="78"/>
+    <cfRule type="duplicateValues" dxfId="59" priority="79"/>
+    <cfRule type="duplicateValues" dxfId="58" priority="80"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2753">
-    <cfRule type="duplicateValues" dxfId="57" priority="58"/>
-    <cfRule type="duplicateValues" dxfId="56" priority="57"/>
-    <cfRule type="duplicateValues" dxfId="55" priority="56"/>
-    <cfRule type="duplicateValues" dxfId="54" priority="55"/>
-    <cfRule type="duplicateValues" dxfId="53" priority="54"/>
-    <cfRule type="duplicateValues" dxfId="52" priority="53"/>
-    <cfRule type="duplicateValues" dxfId="51" priority="52"/>
-    <cfRule type="duplicateValues" dxfId="50" priority="51"/>
-    <cfRule type="duplicateValues" dxfId="49" priority="50"/>
-    <cfRule type="duplicateValues" dxfId="48" priority="49"/>
-    <cfRule type="duplicateValues" dxfId="47" priority="48"/>
-    <cfRule type="duplicateValues" dxfId="46" priority="47"/>
-    <cfRule type="duplicateValues" dxfId="45" priority="46"/>
-    <cfRule type="duplicateValues" dxfId="44" priority="45"/>
-    <cfRule type="duplicateValues" dxfId="43" priority="44"/>
-    <cfRule type="duplicateValues" dxfId="42" priority="43"/>
-    <cfRule type="duplicateValues" dxfId="41" priority="61"/>
+  <conditionalFormatting sqref="A2753">
+    <cfRule type="duplicateValues" dxfId="57" priority="43"/>
+    <cfRule type="duplicateValues" dxfId="56" priority="44"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="45"/>
+    <cfRule type="duplicateValues" dxfId="54" priority="46"/>
+    <cfRule type="duplicateValues" dxfId="53" priority="47"/>
+    <cfRule type="duplicateValues" dxfId="52" priority="48"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="49"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="50"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="51"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="52"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="53"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="54"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="55"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="56"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="57"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="58"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="59"/>
     <cfRule type="duplicateValues" dxfId="40" priority="60"/>
-    <cfRule type="duplicateValues" dxfId="39" priority="59"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="61"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2754">
-    <cfRule type="duplicateValues" dxfId="38" priority="39"/>
-    <cfRule type="duplicateValues" dxfId="37" priority="38"/>
-    <cfRule type="duplicateValues" dxfId="36" priority="37"/>
-    <cfRule type="duplicateValues" dxfId="35" priority="36"/>
-    <cfRule type="duplicateValues" dxfId="34" priority="35"/>
-    <cfRule type="duplicateValues" dxfId="33" priority="34"/>
-    <cfRule type="duplicateValues" dxfId="32" priority="25"/>
-    <cfRule type="duplicateValues" dxfId="31" priority="24"/>
-    <cfRule type="duplicateValues" dxfId="30" priority="42"/>
+  <conditionalFormatting sqref="A2754">
+    <cfRule type="duplicateValues" dxfId="38" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="32"/>
     <cfRule type="duplicateValues" dxfId="29" priority="33"/>
-    <cfRule type="duplicateValues" dxfId="28" priority="32"/>
-    <cfRule type="duplicateValues" dxfId="27" priority="31"/>
-    <cfRule type="duplicateValues" dxfId="26" priority="30"/>
-    <cfRule type="duplicateValues" dxfId="25" priority="29"/>
-    <cfRule type="duplicateValues" dxfId="24" priority="28"/>
-    <cfRule type="duplicateValues" dxfId="23" priority="27"/>
-    <cfRule type="duplicateValues" dxfId="22" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="40"/>
     <cfRule type="duplicateValues" dxfId="21" priority="41"/>
-    <cfRule type="duplicateValues" dxfId="20" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="42"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2758">
-    <cfRule type="duplicateValues" dxfId="19" priority="22"/>
-    <cfRule type="duplicateValues" dxfId="18" priority="21"/>
-    <cfRule type="duplicateValues" dxfId="17" priority="20"/>
-    <cfRule type="duplicateValues" dxfId="16" priority="19"/>
-    <cfRule type="duplicateValues" dxfId="15" priority="18"/>
-    <cfRule type="duplicateValues" dxfId="14" priority="17"/>
-    <cfRule type="duplicateValues" dxfId="13" priority="16"/>
-    <cfRule type="duplicateValues" dxfId="12" priority="15"/>
-    <cfRule type="duplicateValues" dxfId="11" priority="14"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="13"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="12"/>
-    <cfRule type="duplicateValues" dxfId="8" priority="11"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="4"/>
-    <cfRule type="duplicateValues" dxfId="5" priority="10"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="9"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="8"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="7"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="6"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
+  <conditionalFormatting sqref="A2758">
+    <cfRule type="duplicateValues" dxfId="19" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="22"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
